--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_8sep26_Tue.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_8sep26_Tue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99EEBE7-7B83-48E6-8CAF-59FE5E092384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0204C281-7EB9-4089-9CB6-D2074BF99806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3195" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3196" uniqueCount="284">
   <si>
     <t>Date</t>
   </si>
@@ -1061,7 +1061,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1233,12 +1233,6 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="22" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1281,6 +1275,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1646,7 +1643,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -1681,13 +1678,13 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B2, $C$2:$C$785, C2, $D$2:$D$785, D2, $E$2:$E$785, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$785, B2, $C$2:$C$785, C2, $D$2:$D$785, D2, $E$2:$E$785, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
       <c r="P2" s="10"/>
     </row>
-    <row r="3" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>62</v>
       </c>
@@ -1720,13 +1717,13 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B3, $C$2:$C$785, C3, $D$2:$D$785, D3, $E$2:$E$785, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
     </row>
-    <row r="4" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -1759,13 +1756,13 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B4, $C$2:$C$785, C4, $D$2:$D$785, D4, $E$2:$E$785, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
     </row>
-    <row r="5" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -1807,13 +1804,13 @@
         <v>250</v>
       </c>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B5, $C$2:$C$785, C5, $D$2:$D$785, D5, $E$2:$E$785, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
     </row>
-    <row r="6" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>62</v>
       </c>
@@ -1846,13 +1843,13 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B6, $C$2:$C$785, C6, $D$2:$D$785, D6, $E$2:$E$785, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="26"/>
       <c r="P6" s="10"/>
     </row>
-    <row r="7" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
         <v>62</v>
       </c>
@@ -1885,13 +1882,13 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B7, $C$2:$C$785, C7, $D$2:$D$785, D7, $E$2:$E$785, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="10"/>
       <c r="P7" s="10"/>
     </row>
-    <row r="8" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -1926,13 +1923,13 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B8, $C$2:$C$785, C8, $D$2:$D$785, D8, $E$2:$E$785, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
     </row>
-    <row r="9" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="6" t="s">
         <v>62</v>
       </c>
@@ -1965,13 +1962,13 @@
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B9, $C$2:$C$785, C9, $D$2:$D$785, D9, $E$2:$E$785, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="10"/>
       <c r="P9" s="25"/>
     </row>
-    <row r="10" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
         <v>62</v>
       </c>
@@ -2004,13 +2001,13 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B10, $C$2:$C$785, C10, $D$2:$D$785, D10, $E$2:$E$785, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
     </row>
-    <row r="11" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
         <v>62</v>
       </c>
@@ -2043,13 +2040,13 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B11, $C$2:$C$785, C11, $D$2:$D$785, D11, $E$2:$E$785, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
     </row>
-    <row r="12" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>62</v>
       </c>
@@ -2082,13 +2079,13 @@
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B12, $C$2:$C$785, C12, $D$2:$D$785, D12, $E$2:$E$785, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
     </row>
-    <row r="13" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="6" t="s">
         <v>62</v>
       </c>
@@ -2121,13 +2118,13 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B13, $C$2:$C$785, C13, $D$2:$D$785, D13, $E$2:$E$785, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="10"/>
       <c r="P13" s="26"/>
     </row>
-    <row r="14" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
         <v>62</v>
       </c>
@@ -2160,13 +2157,13 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B14, $C$2:$C$785, C14, $D$2:$D$785, D14, $E$2:$E$785, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14" s="19"/>
       <c r="P14" s="10"/>
     </row>
-    <row r="15" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="3">
         <v>46252.6875</v>
       </c>
@@ -2201,13 +2198,13 @@
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B15, $C$2:$C$785, C15, $D$2:$D$785, D15, $E$2:$E$785, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O15" s="10"/>
       <c r="P15" s="10"/>
     </row>
-    <row r="16" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3">
         <v>46268.385416666664</v>
       </c>
@@ -2249,13 +2246,13 @@
         <v>500</v>
       </c>
       <c r="N16" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B16, $C$2:$C$785, C16, $D$2:$D$785, D16, $E$2:$E$785, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
     </row>
-    <row r="17" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
         <v>46269.375</v>
       </c>
@@ -2297,13 +2294,13 @@
         <v>300</v>
       </c>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B17, $C$2:$C$785, C17, $D$2:$D$785, D17, $E$2:$E$785, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17" s="10"/>
       <c r="P17" s="10"/>
     </row>
-    <row r="18" spans="1:16" s="34" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:16" s="34" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="6" t="s">
         <v>62</v>
       </c>
@@ -2336,13 +2333,13 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B18, $C$2:$C$785, C18, $D$2:$D$785, D18, $E$2:$E$785, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18" s="10"/>
       <c r="P18" s="10"/>
     </row>
-    <row r="19" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -2377,13 +2374,13 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B19, $C$2:$C$785, C19, $D$2:$D$785, D19, $E$2:$E$785, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
     </row>
-    <row r="20" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="6" t="s">
         <v>62</v>
       </c>
@@ -2416,13 +2413,13 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B20, $C$2:$C$785, C20, $D$2:$D$785, D20, $E$2:$E$785, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20" s="10"/>
       <c r="P20" s="10"/>
     </row>
-    <row r="21" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3">
         <v>46261.375</v>
       </c>
@@ -2464,13 +2461,13 @@
         <v>300</v>
       </c>
       <c r="N21" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B21, $C$2:$C$785, C21, $D$2:$D$785, D21, $E$2:$E$785, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21" s="25"/>
       <c r="P21" s="10"/>
     </row>
-    <row r="22" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="3">
         <v>46031.4375</v>
       </c>
@@ -2508,7 +2505,7 @@
         <v>3156</v>
       </c>
       <c r="N22" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B22, $C$2:$C$785, C22, $D$2:$D$785, D22, $E$2:$E$785, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22" s="10"/>
@@ -2557,12 +2554,12 @@
         <v>650</v>
       </c>
       <c r="N23" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B23, $C$2:$C$785, C23, $D$2:$D$785, D23, $E$2:$E$785, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P23" s="10"/>
     </row>
-    <row r="24" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="6" t="s">
         <v>62</v>
       </c>
@@ -2595,13 +2592,13 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B24, $C$2:$C$785, C24, $D$2:$D$785, D24, $E$2:$E$785, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24" s="10"/>
       <c r="P24" s="10"/>
     </row>
-    <row r="25" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -2643,13 +2640,13 @@
         <v>450</v>
       </c>
       <c r="N25" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B25, $C$2:$C$785, C25, $D$2:$D$785, D25, $E$2:$E$785, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25" s="10"/>
       <c r="P25" s="10"/>
     </row>
-    <row r="26" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -2682,13 +2679,13 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B26, $C$2:$C$785, C26, $D$2:$D$785, D26, $E$2:$E$785, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26" s="10"/>
       <c r="P26" s="10"/>
     </row>
-    <row r="27" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="6" t="s">
         <v>62</v>
       </c>
@@ -2721,13 +2718,13 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B27, $C$2:$C$785, C27, $D$2:$D$785, D27, $E$2:$E$785, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27" s="10"/>
       <c r="P27" s="10"/>
     </row>
-    <row r="28" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="6" t="s">
         <v>62</v>
       </c>
@@ -2762,12 +2759,12 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B28, $C$2:$C$785, C28, $D$2:$D$785, D28, $E$2:$E$785, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P28" s="10"/>
     </row>
-    <row r="29" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="6" t="s">
         <v>62</v>
       </c>
@@ -2802,13 +2799,13 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B29, $C$2:$C$785, C29, $D$2:$D$785, D29, $E$2:$E$785, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29" s="10"/>
       <c r="P29" s="10"/>
     </row>
-    <row r="30" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="3">
         <v>46268.375</v>
       </c>
@@ -2850,13 +2847,13 @@
         <v>516</v>
       </c>
       <c r="N30" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B30, $C$2:$C$785, C30, $D$2:$D$785, D30, $E$2:$E$785, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30" s="10"/>
       <c r="P30" s="10"/>
     </row>
-    <row r="31" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3">
         <v>46252.6875</v>
       </c>
@@ -2891,12 +2888,12 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B31, $C$2:$C$785, C31, $D$2:$D$785, D31, $E$2:$E$785, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P31" s="10"/>
     </row>
-    <row r="32" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="3">
         <v>46261.375</v>
       </c>
@@ -2938,13 +2935,13 @@
         <v>300</v>
       </c>
       <c r="N32" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B32, $C$2:$C$785, C32, $D$2:$D$785, D32, $E$2:$E$785, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32" s="10"/>
       <c r="P32" s="25"/>
     </row>
-    <row r="33" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="6" t="s">
         <v>62</v>
       </c>
@@ -2977,13 +2974,13 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B33, $C$2:$C$785, C33, $D$2:$D$785, D33, $E$2:$E$785, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33" s="10"/>
       <c r="P33" s="10"/>
     </row>
-    <row r="34" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3">
         <v>46262.457638888889</v>
       </c>
@@ -3025,13 +3022,13 @@
         <v>222.75</v>
       </c>
       <c r="N34" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B34, $C$2:$C$785, C34, $D$2:$D$785, D34, $E$2:$E$785, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34" s="10"/>
       <c r="P34" s="10"/>
     </row>
-    <row r="35" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3064,13 +3061,13 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B35, $C$2:$C$785, C35, $D$2:$D$785, D35, $E$2:$E$785, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35" s="10"/>
       <c r="P35" s="10"/>
     </row>
-    <row r="36" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="6" t="s">
         <v>62</v>
       </c>
@@ -3103,13 +3100,13 @@
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B36, $C$2:$C$785, C36, $D$2:$D$785, D36, $E$2:$E$785, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36" s="10"/>
       <c r="P36" s="10"/>
     </row>
-    <row r="37" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3144,13 +3141,13 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B37, $C$2:$C$785, C37, $D$2:$D$785, D37, $E$2:$E$785, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37" s="10"/>
       <c r="P37" s="10"/>
     </row>
-    <row r="38" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="3">
         <v>46252.6875</v>
       </c>
@@ -3183,13 +3180,13 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B38, $C$2:$C$785, C38, $D$2:$D$785, D38, $E$2:$E$785, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38" s="10"/>
       <c r="P38" s="10"/>
     </row>
-    <row r="39" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="3">
         <v>46260.375</v>
       </c>
@@ -3231,13 +3228,13 @@
         <v>300</v>
       </c>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B39, $C$2:$C$785, C39, $D$2:$D$785, D39, $E$2:$E$785, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39" s="10"/>
       <c r="P39" s="10"/>
     </row>
-    <row r="40" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="3">
         <v>46261.375</v>
       </c>
@@ -3279,13 +3276,13 @@
         <v>300</v>
       </c>
       <c r="N40" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B40, $C$2:$C$785, C40, $D$2:$D$785, D40, $E$2:$E$785, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40" s="10"/>
       <c r="P40" s="10"/>
     </row>
-    <row r="41" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="6" t="s">
         <v>62</v>
       </c>
@@ -3318,12 +3315,12 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B41, $C$2:$C$785, C41, $D$2:$D$785, D41, $E$2:$E$785, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P41" s="10"/>
     </row>
-    <row r="42" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="3">
         <v>46269.375</v>
       </c>
@@ -3365,12 +3362,12 @@
         <v>460</v>
       </c>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B42, $C$2:$C$785, C42, $D$2:$D$785, D42, $E$2:$E$785, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P42" s="10"/>
     </row>
-    <row r="43" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="6" t="s">
         <v>62</v>
       </c>
@@ -3403,12 +3400,12 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B43, $C$2:$C$785, C43, $D$2:$D$785, D43, $E$2:$E$785, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P43" s="10"/>
     </row>
-    <row r="44" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3441,13 +3438,13 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B44, $C$2:$C$785, C44, $D$2:$D$785, D44, $E$2:$E$785, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44" s="25"/>
       <c r="P44" s="10"/>
     </row>
-    <row r="45" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="3">
         <v>46252.6875</v>
       </c>
@@ -3482,12 +3479,12 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B45, $C$2:$C$785, C45, $D$2:$D$785, D45, $E$2:$E$785, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45" s="10"/>
     </row>
-    <row r="46" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="6" t="s">
         <v>62</v>
       </c>
@@ -3522,11 +3519,11 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B46, $C$2:$C$785, C46, $D$2:$D$785, D46, $E$2:$E$785, E46) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3561,12 +3558,12 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B47, $C$2:$C$785, C47, $D$2:$D$785, D47, $E$2:$E$785, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47" s="10"/>
     </row>
-    <row r="48" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="6" t="s">
         <v>62</v>
       </c>
@@ -3601,7 +3598,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B48, $C$2:$C$785, C48, $D$2:$D$785, D48, $E$2:$E$785, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3648,11 +3645,11 @@
         <v>540</v>
       </c>
       <c r="N49" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B49, $C$2:$C$785, C49, $D$2:$D$785, D49, $E$2:$E$785, E49) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="20">
         <v>46255</v>
       </c>
@@ -3694,11 +3691,11 @@
         <v>300</v>
       </c>
       <c r="N50" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B50, $C$2:$C$785, C50, $D$2:$D$785, D50, $E$2:$E$785, E50) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="6" t="s">
         <v>62</v>
       </c>
@@ -3731,12 +3728,12 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B51, $C$2:$C$785, C51, $D$2:$D$785, D51, $E$2:$E$785, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51" s="34"/>
     </row>
-    <row r="52" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="6" t="s">
         <v>62</v>
       </c>
@@ -3771,11 +3768,11 @@
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B52, $C$2:$C$785, C52, $D$2:$D$785, D52, $E$2:$E$785, E52) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="6" t="s">
         <v>62</v>
       </c>
@@ -3810,13 +3807,13 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B53, $C$2:$C$785, C53, $D$2:$D$785, D53, $E$2:$E$785, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O53"/>
       <c r="P53"/>
     </row>
-    <row r="54" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3849,13 +3846,13 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B54, $C$2:$C$785, C54, $D$2:$D$785, D54, $E$2:$E$785, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
       <c r="P54"/>
     </row>
-    <row r="55" spans="1:16" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:16" ht="16.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3888,13 +3885,13 @@
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B55, $C$2:$C$785, C55, $D$2:$D$785, D55, $E$2:$E$785, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
       <c r="P55"/>
     </row>
-    <row r="56" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="6" t="s">
         <v>62</v>
       </c>
@@ -3927,13 +3924,13 @@
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B56, $C$2:$C$785, C56, $D$2:$D$785, D56, $E$2:$E$785, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56"/>
       <c r="P56"/>
     </row>
-    <row r="57" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -3966,13 +3963,13 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B57, $C$2:$C$785, C57, $D$2:$D$785, D57, $E$2:$E$785, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57"/>
       <c r="P57"/>
     </row>
-    <row r="58" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="6" t="s">
         <v>62</v>
       </c>
@@ -4005,13 +4002,13 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B58, $C$2:$C$785, C58, $D$2:$D$785, D58, $E$2:$E$785, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58"/>
       <c r="P58"/>
     </row>
-    <row r="59" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -4044,13 +4041,13 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B59, $C$2:$C$785, C59, $D$2:$D$785, D59, $E$2:$E$785, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59"/>
       <c r="P59"/>
     </row>
-    <row r="60" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
@@ -4083,13 +4080,13 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B60, $C$2:$C$785, C60, $D$2:$D$785, D60, $E$2:$E$785, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60"/>
       <c r="P60"/>
     </row>
-    <row r="61" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="6" t="s">
         <v>62</v>
       </c>
@@ -4122,13 +4119,13 @@
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B61, $C$2:$C$785, C61, $D$2:$D$785, D61, $E$2:$E$785, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61"/>
       <c r="P61"/>
     </row>
-    <row r="62" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="6" t="s">
         <v>62</v>
       </c>
@@ -4161,12 +4158,12 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B62, $C$2:$C$785, C62, $D$2:$D$785, D62, $E$2:$E$785, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P62"/>
     </row>
-    <row r="63" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="6" t="s">
         <v>62</v>
       </c>
@@ -4199,13 +4196,13 @@
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B63, $C$2:$C$785, C63, $D$2:$D$785, D63, $E$2:$E$785, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63"/>
       <c r="P63"/>
     </row>
-    <row r="64" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="6" t="s">
         <v>62</v>
       </c>
@@ -4240,13 +4237,13 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B64, $C$2:$C$785, C64, $D$2:$D$785, D64, $E$2:$E$785, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64"/>
       <c r="P64"/>
     </row>
-    <row r="65" spans="1:16" s="25" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:16" s="25" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="3">
         <v>46258.601388888892</v>
       </c>
@@ -4288,13 +4285,13 @@
         <v>300</v>
       </c>
       <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B65, $C$2:$C$785, C65, $D$2:$D$785, D65, $E$2:$E$785, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O65"/>
       <c r="P65"/>
     </row>
-    <row r="66" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="6" t="s">
         <v>62</v>
       </c>
@@ -4327,13 +4324,13 @@
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B66, $C$2:$C$785, C66, $D$2:$D$785, D66, $E$2:$E$785, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$785, B66, $C$2:$C$785, C66, $D$2:$D$785, D66, $E$2:$E$785, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O66"/>
       <c r="P66"/>
     </row>
-    <row r="67" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="6" t="s">
         <v>62</v>
       </c>
@@ -4366,13 +4363,13 @@
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B67, $C$2:$C$785, C67, $D$2:$D$785, D67, $E$2:$E$785, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O67"/>
       <c r="P67"/>
     </row>
-    <row r="68" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="3">
         <v>46252.6875</v>
       </c>
@@ -4407,13 +4404,13 @@
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B68, $C$2:$C$785, C68, $D$2:$D$785, D68, $E$2:$E$785, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68"/>
       <c r="P68"/>
     </row>
-    <row r="69" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="6" t="s">
         <v>62</v>
       </c>
@@ -4448,13 +4445,13 @@
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B69, $C$2:$C$785, C69, $D$2:$D$785, D69, $E$2:$E$785, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O69"/>
       <c r="P69"/>
     </row>
-    <row r="70" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="6" t="s">
         <v>62</v>
       </c>
@@ -4489,13 +4486,13 @@
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B70, $C$2:$C$785, C70, $D$2:$D$785, D70, $E$2:$E$785, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O70"/>
       <c r="P70"/>
     </row>
-    <row r="71" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="6" t="s">
         <v>62</v>
       </c>
@@ -4528,13 +4525,13 @@
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
       <c r="N71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B71, $C$2:$C$785, C71, $D$2:$D$785, D71, $E$2:$E$785, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O71"/>
       <c r="P71"/>
     </row>
-    <row r="72" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="3">
         <v>46252.6875</v>
       </c>
@@ -4569,13 +4566,13 @@
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B72, $C$2:$C$785, C72, $D$2:$D$785, D72, $E$2:$E$785, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O72"/>
       <c r="P72"/>
     </row>
-    <row r="73" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="3">
         <v>46254.375</v>
       </c>
@@ -4612,13 +4609,13 @@
       <c r="L73" s="17"/>
       <c r="M73" s="17"/>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B73, $C$2:$C$785, C73, $D$2:$D$785, D73, $E$2:$E$785, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O73"/>
       <c r="P73"/>
     </row>
-    <row r="74" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="6" t="s">
         <v>62</v>
       </c>
@@ -4651,13 +4648,13 @@
       <c r="L74" s="17"/>
       <c r="M74" s="17"/>
       <c r="N74" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B74, $C$2:$C$785, C74, $D$2:$D$785, D74, $E$2:$E$785, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O74"/>
       <c r="P74"/>
     </row>
-    <row r="75" spans="1:16" s="19" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:16" s="19" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="3">
         <v>46267.375</v>
       </c>
@@ -4699,13 +4696,13 @@
         <v>300</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B75, $C$2:$C$785, C75, $D$2:$D$785, D75, $E$2:$E$785, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O75"/>
       <c r="P75"/>
     </row>
-    <row r="76" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="6" t="s">
         <v>62</v>
       </c>
@@ -4738,13 +4735,13 @@
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B76, $C$2:$C$785, C76, $D$2:$D$785, D76, $E$2:$E$785, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O76"/>
       <c r="P76"/>
     </row>
-    <row r="77" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="6" t="s">
         <v>62</v>
       </c>
@@ -4779,13 +4776,13 @@
       <c r="L77" s="17"/>
       <c r="M77" s="17"/>
       <c r="N77" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B77, $C$2:$C$785, C77, $D$2:$D$785, D77, $E$2:$E$785, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O77"/>
       <c r="P77"/>
     </row>
-    <row r="78" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="6" t="s">
         <v>62</v>
       </c>
@@ -4818,13 +4815,13 @@
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B78, $C$2:$C$785, C78, $D$2:$D$785, D78, $E$2:$E$785, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78"/>
       <c r="P78"/>
     </row>
-    <row r="79" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="6" t="s">
         <v>62</v>
       </c>
@@ -4857,13 +4854,13 @@
       <c r="L79" s="17"/>
       <c r="M79" s="17"/>
       <c r="N79" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B79, $C$2:$C$785, C79, $D$2:$D$785, D79, $E$2:$E$785, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O79"/>
       <c r="P79" s="34"/>
     </row>
-    <row r="80" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="6" t="s">
         <v>62</v>
       </c>
@@ -4896,13 +4893,13 @@
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
       <c r="N80" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B80, $C$2:$C$785, C80, $D$2:$D$785, D80, $E$2:$E$785, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O80"/>
       <c r="P80"/>
     </row>
-    <row r="81" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="29">
         <v>46255</v>
       </c>
@@ -4944,13 +4941,13 @@
         <v>442</v>
       </c>
       <c r="N81" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B81, $C$2:$C$785, C81, $D$2:$D$785, D81, $E$2:$E$785, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O81"/>
       <c r="P81"/>
     </row>
-    <row r="82" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="6" t="s">
         <v>62</v>
       </c>
@@ -4985,13 +4982,13 @@
       <c r="L82" s="17"/>
       <c r="M82" s="17"/>
       <c r="N82" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B82, $C$2:$C$785, C82, $D$2:$D$785, D82, $E$2:$E$785, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O82"/>
       <c r="P82"/>
     </row>
-    <row r="83" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -5024,13 +5021,13 @@
       <c r="L83" s="17"/>
       <c r="M83" s="17"/>
       <c r="N83" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B83, $C$2:$C$785, C83, $D$2:$D$785, D83, $E$2:$E$785, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O83"/>
       <c r="P83"/>
     </row>
-    <row r="84" spans="1:16" s="26" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:16" s="26" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="6" t="s">
         <v>62</v>
       </c>
@@ -5063,13 +5060,13 @@
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B84, $C$2:$C$785, C84, $D$2:$D$785, D84, $E$2:$E$785, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O84"/>
       <c r="P84"/>
     </row>
-    <row r="85" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="6" t="s">
         <v>62</v>
       </c>
@@ -5104,13 +5101,13 @@
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
       <c r="N85" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B85, $C$2:$C$785, C85, $D$2:$D$785, D85, $E$2:$E$785, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O85"/>
       <c r="P85"/>
     </row>
-    <row r="86" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="6" t="s">
         <v>62</v>
       </c>
@@ -5143,13 +5140,13 @@
       <c r="L86" s="17"/>
       <c r="M86" s="17"/>
       <c r="N86" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B86, $C$2:$C$785, C86, $D$2:$D$785, D86, $E$2:$E$785, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O86"/>
       <c r="P86"/>
     </row>
-    <row r="87" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="6" t="s">
         <v>62</v>
       </c>
@@ -5182,13 +5179,13 @@
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
       <c r="N87" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B87, $C$2:$C$785, C87, $D$2:$D$785, D87, $E$2:$E$785, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O87"/>
       <c r="P87"/>
     </row>
-    <row r="88" spans="1:16" s="25" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:16" s="25" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="6" t="s">
         <v>62</v>
       </c>
@@ -5221,13 +5218,13 @@
       <c r="L88" s="17"/>
       <c r="M88" s="17"/>
       <c r="N88" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B88, $C$2:$C$785, C88, $D$2:$D$785, D88, $E$2:$E$785, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O88"/>
       <c r="P88"/>
     </row>
-    <row r="89" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="6" t="s">
         <v>62</v>
       </c>
@@ -5260,13 +5257,13 @@
       <c r="L89" s="17"/>
       <c r="M89" s="17"/>
       <c r="N89" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B89, $C$2:$C$785, C89, $D$2:$D$785, D89, $E$2:$E$785, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O89"/>
       <c r="P89"/>
     </row>
-    <row r="90" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="6" t="s">
         <v>62</v>
       </c>
@@ -5299,13 +5296,13 @@
       <c r="L90" s="17"/>
       <c r="M90" s="17"/>
       <c r="N90" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B90, $C$2:$C$785, C90, $D$2:$D$785, D90, $E$2:$E$785, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O90"/>
       <c r="P90"/>
     </row>
-    <row r="91" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="6" t="s">
         <v>62</v>
       </c>
@@ -5338,13 +5335,13 @@
       <c r="L91" s="17"/>
       <c r="M91" s="17"/>
       <c r="N91" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B91, $C$2:$C$785, C91, $D$2:$D$785, D91, $E$2:$E$785, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O91"/>
       <c r="P91"/>
     </row>
-    <row r="92" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="6" t="s">
         <v>62</v>
       </c>
@@ -5377,13 +5374,13 @@
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
       <c r="N92" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B92, $C$2:$C$785, C92, $D$2:$D$785, D92, $E$2:$E$785, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O92"/>
       <c r="P92"/>
     </row>
-    <row r="93" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -5416,13 +5413,13 @@
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
       <c r="N93" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B93, $C$2:$C$785, C93, $D$2:$D$785, D93, $E$2:$E$785, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O93"/>
       <c r="P93"/>
     </row>
-    <row r="94" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="6" t="s">
         <v>62</v>
       </c>
@@ -5455,13 +5452,13 @@
       <c r="L94" s="17"/>
       <c r="M94" s="17"/>
       <c r="N94" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B94, $C$2:$C$785, C94, $D$2:$D$785, D94, $E$2:$E$785, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O94"/>
       <c r="P94"/>
     </row>
-    <row r="95" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="6" t="s">
         <v>62</v>
       </c>
@@ -5496,13 +5493,13 @@
       <c r="L95" s="17"/>
       <c r="M95" s="17"/>
       <c r="N95" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B95, $C$2:$C$785, C95, $D$2:$D$785, D95, $E$2:$E$785, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O95"/>
       <c r="P95"/>
     </row>
-    <row r="96" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="6" t="s">
         <v>62</v>
       </c>
@@ -5535,13 +5532,13 @@
       <c r="L96" s="17"/>
       <c r="M96" s="17"/>
       <c r="N96" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B96, $C$2:$C$785, C96, $D$2:$D$785, D96, $E$2:$E$785, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O96"/>
       <c r="P96"/>
     </row>
-    <row r="97" spans="1:16" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:16" ht="15.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="6" t="s">
         <v>62</v>
       </c>
@@ -5574,7 +5571,7 @@
       <c r="L97" s="17"/>
       <c r="M97" s="17"/>
       <c r="N97" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B97, $C$2:$C$785, C97, $D$2:$D$785, D97, $E$2:$E$785, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O97"/>
@@ -5618,11 +5615,11 @@
         <v>8480</v>
       </c>
       <c r="M98" s="27">
-        <f>ABS((D98*E98)-L98)</f>
+        <f t="shared" ref="M98:M107" si="2">ABS((D98*E98)-L98)</f>
         <v>280</v>
       </c>
       <c r="N98" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B98, $C$2:$C$785, C98, $D$2:$D$785, D98, $E$2:$E$785, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O98" s="47" t="s">
@@ -5667,11 +5664,11 @@
         <v>15050</v>
       </c>
       <c r="M99" s="18">
-        <f>ABS((D99*E99)-L99)</f>
+        <f t="shared" si="2"/>
         <v>430</v>
       </c>
       <c r="N99" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B99, $C$2:$C$785, C99, $D$2:$D$785, D99, $E$2:$E$785, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O99" s="47" t="s">
@@ -5716,12 +5713,15 @@
         <v>9170</v>
       </c>
       <c r="M100" s="33">
-        <f>ABS((D100*E100)-L100)</f>
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B100, $C$2:$C$785, C100, $D$2:$D$785, D100, $E$2:$E$785, E100) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O100" s="47" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5762,11 +5762,11 @@
         <v>9170</v>
       </c>
       <c r="M101" s="33">
-        <f>ABS((D101*E101)-L101)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B101, $C$2:$C$785, C101, $D$2:$D$785, D101, $E$2:$E$785, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5808,11 +5808,11 @@
         <v>5755</v>
       </c>
       <c r="M102" s="33">
-        <f>ABS((D102*E102)-L102)</f>
+        <f t="shared" si="2"/>
         <v>275</v>
       </c>
       <c r="N102" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B102, $C$2:$C$785, C102, $D$2:$D$785, D102, $E$2:$E$785, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O102" s="47" t="s">
@@ -5857,11 +5857,11 @@
         <v>5805</v>
       </c>
       <c r="M103" s="33">
-        <f>ABS((D103*E103)-L103)</f>
+        <f t="shared" si="2"/>
         <v>225</v>
       </c>
       <c r="N103" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B103, $C$2:$C$785, C103, $D$2:$D$785, D103, $E$2:$E$785, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O103" s="47" t="s">
@@ -5906,11 +5906,11 @@
         <v>19730.5</v>
       </c>
       <c r="M104" s="33">
-        <f>ABS((D104*E104)-L104)</f>
+        <f t="shared" si="2"/>
         <v>504.5</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B104, $C$2:$C$785, C104, $D$2:$D$785, D104, $E$2:$E$785, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5952,11 +5952,11 @@
         <v>5940</v>
       </c>
       <c r="M105" s="18">
-        <f>ABS((D105*E105)-L105)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B105, $C$2:$C$785, C105, $D$2:$D$785, D105, $E$2:$E$785, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O105" s="47" t="s">
@@ -6001,11 +6001,11 @@
         <v>25300</v>
       </c>
       <c r="M106" s="18">
-        <f>ABS((D106*E106)-L106)</f>
+        <f t="shared" si="2"/>
         <v>650</v>
       </c>
       <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B106, $C$2:$C$785, C106, $D$2:$D$785, D106, $E$2:$E$785, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O106" s="47" t="s">
@@ -6050,11 +6050,11 @@
         <v>12480</v>
       </c>
       <c r="M107" s="18">
-        <f>ABS((D107*E107)-L107)</f>
+        <f t="shared" si="2"/>
         <v>495</v>
       </c>
       <c r="N107" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B107, $C$2:$C$785, C107, $D$2:$D$785, D107, $E$2:$E$785, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O107" s="47" t="s">
@@ -6089,14 +6089,14 @@
       <c r="I108" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J108" s="60" t="s">
+      <c r="J108" s="40" t="s">
         <v>118</v>
       </c>
       <c r="K108" s="18"/>
       <c r="L108" s="18"/>
       <c r="M108" s="18"/>
       <c r="N108" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B108, $C$2:$C$785, C108, $D$2:$D$785, D108, $E$2:$E$785, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O108" s="47" t="s">
@@ -6145,7 +6145,7 @@
         <v>710.99999999999636</v>
       </c>
       <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B109, $C$2:$C$785, C109, $D$2:$D$785, D109, $E$2:$E$785, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="10"/>
@@ -6192,7 +6192,7 @@
         <v>1567.5</v>
       </c>
       <c r="N110" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B110, $C$2:$C$785, C110, $D$2:$D$785, D110, $E$2:$E$785, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O110" s="47" t="s">
@@ -6227,7 +6227,7 @@
       <c r="I111" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J111" s="59" t="s">
+      <c r="J111" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K111" s="18" t="s">
@@ -6241,7 +6241,7 @@
         <v>450</v>
       </c>
       <c r="N111" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B111, $C$2:$C$785, C111, $D$2:$D$785, D111, $E$2:$E$785, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O111" s="47" t="s">
@@ -6290,7 +6290,7 @@
         <v>300</v>
       </c>
       <c r="N112" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B112, $C$2:$C$785, C112, $D$2:$D$785, D112, $E$2:$E$785, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O112" s="47" t="s">
@@ -6330,7 +6330,7 @@
       <c r="L113" s="18"/>
       <c r="M113" s="18"/>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B113, $C$2:$C$785, C113, $D$2:$D$785, D113, $E$2:$E$785, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O113" s="47" t="s">
@@ -6375,11 +6375,11 @@
         <v>25530</v>
       </c>
       <c r="M114" s="18">
-        <f>ABS((D114*E114)-L114)</f>
+        <f t="shared" ref="M114:M123" si="3">ABS((D114*E114)-L114)</f>
         <v>650</v>
       </c>
       <c r="N114" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B114, $C$2:$C$785, C114, $D$2:$D$785, D114, $E$2:$E$785, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6421,11 +6421,11 @@
         <v>3560</v>
       </c>
       <c r="M115" s="33">
-        <f>ABS((D115*E115)-L115)</f>
+        <f t="shared" si="3"/>
         <v>175</v>
       </c>
       <c r="N115" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B115, $C$2:$C$785, C115, $D$2:$D$785, D115, $E$2:$E$785, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O115" s="47" t="s">
@@ -6470,11 +6470,11 @@
         <v>3510</v>
       </c>
       <c r="M116" s="33">
-        <f>ABS((D116*E116)-L116)</f>
+        <f t="shared" si="3"/>
         <v>225</v>
       </c>
       <c r="N116" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B116, $C$2:$C$785, C116, $D$2:$D$785, D116, $E$2:$E$785, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O116" s="47" t="s">
@@ -6519,11 +6519,11 @@
         <v>8810</v>
       </c>
       <c r="M117" s="18">
-        <f>ABS((D117*E117)-L117)</f>
+        <f t="shared" si="3"/>
         <v>650</v>
       </c>
       <c r="N117" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B117, $C$2:$C$785, C117, $D$2:$D$785, D117, $E$2:$E$785, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="47" t="s">
@@ -6568,11 +6568,11 @@
         <v>20260</v>
       </c>
       <c r="M118" s="18">
-        <f>ABS((D118*E118)-L118)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N118" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B118, $C$2:$C$785, C118, $D$2:$D$785, D118, $E$2:$E$785, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O118"/>
@@ -6615,12 +6615,15 @@
         <v>16219.999999999998</v>
       </c>
       <c r="M119" s="33">
-        <f>ABS((D119*E119)-L119)</f>
+        <f t="shared" si="3"/>
         <v>300.00000000000182</v>
       </c>
       <c r="N119" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B119, $C$2:$C$785, C119, $D$2:$D$785, D119, $E$2:$E$785, E119) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O119" s="47" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="120" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6661,12 +6664,15 @@
         <v>6334</v>
       </c>
       <c r="M120" s="33">
-        <f>ABS((D120*E120)-L120)</f>
+        <f t="shared" si="3"/>
         <v>274</v>
       </c>
       <c r="N120" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B120, $C$2:$C$785, C120, $D$2:$D$785, D120, $E$2:$E$785, E120) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O120" s="47" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="121" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6707,11 +6713,11 @@
         <v>12510</v>
       </c>
       <c r="M121" s="18">
-        <f>ABS((D121*E121)-L121)</f>
+        <f t="shared" si="3"/>
         <v>290</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B121, $C$2:$C$785, C121, $D$2:$D$785, D121, $E$2:$E$785, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6753,16 +6759,14 @@
         <v>9270</v>
       </c>
       <c r="M122" s="18">
-        <f>ABS((D122*E122)-L122)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B122, $C$2:$C$785, C122, $D$2:$D$785, D122, $E$2:$E$785, E122) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O122" s="47" t="s">
-        <v>262</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O122" s="74"/>
     </row>
     <row r="123" spans="1:16" s="26" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="11">
@@ -6802,11 +6806,11 @@
         <v>5620</v>
       </c>
       <c r="M123" s="33">
-        <f>ABS((D123*E123)-L123)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B123, $C$2:$C$785, C123, $D$2:$D$785, D123, $E$2:$E$785, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O123" s="10"/>
@@ -6841,7 +6845,7 @@
       </c>
       <c r="J124" s="40"/>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B124, $C$2:$C$785, C124, $D$2:$D$785, D124, $E$2:$E$785, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6883,57 +6887,57 @@
         <v>15075</v>
       </c>
       <c r="M125" s="18">
-        <f>ABS((D125*E125)-L125)</f>
+        <f t="shared" ref="M125:M136" si="4">ABS((D125*E125)-L125)</f>
         <v>645</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B125, $C$2:$C$785, C125, $D$2:$D$785, D125, $E$2:$E$785, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
     <row r="126" spans="1:16" s="25" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="61">
+      <c r="A126" s="59">
         <v>46273.385416666664</v>
       </c>
-      <c r="B126" s="62" t="s">
+      <c r="B126" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="C126" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="D126" s="62">
+      <c r="C126" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="D126" s="60">
         <v>500</v>
       </c>
-      <c r="E126" s="62">
+      <c r="E126" s="60">
         <v>34.659999999999997</v>
       </c>
-      <c r="F126" s="63">
+      <c r="F126" s="61">
         <v>4.052836986</v>
       </c>
-      <c r="G126" s="64" t="s">
+      <c r="G126" s="62" t="s">
         <v>46</v>
       </c>
-      <c r="H126" s="65">
+      <c r="H126" s="63">
         <v>33.31</v>
       </c>
-      <c r="I126" s="66" t="s">
-        <v>8</v>
-      </c>
-      <c r="J126" s="67" t="s">
+      <c r="I126" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="J126" s="65" t="s">
         <v>118</v>
       </c>
-      <c r="K126" s="67" t="s">
+      <c r="K126" s="65" t="s">
         <v>278</v>
       </c>
-      <c r="L126" s="67">
+      <c r="L126" s="65">
         <v>16580</v>
       </c>
-      <c r="M126" s="67">
-        <f>ABS((D126*E126)-L126)</f>
+      <c r="M126" s="65">
+        <f t="shared" si="4"/>
         <v>750</v>
       </c>
       <c r="N126" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B126, $C$2:$C$785, C126, $D$2:$D$785, D126, $E$2:$E$785, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P126" s="25" t="s">
@@ -6978,11 +6982,11 @@
         <v>8220</v>
       </c>
       <c r="M127" s="18">
-        <f>ABS((D127*E127)-L127)</f>
+        <f t="shared" si="4"/>
         <v>360</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B127, $C$2:$C$785, C127, $D$2:$D$785, D127, $E$2:$E$785, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O127" s="47" t="s">
@@ -7027,11 +7031,11 @@
         <v>26020</v>
       </c>
       <c r="M128" s="18">
-        <f>ABS((D128*E128)-L128)</f>
+        <f t="shared" si="4"/>
         <v>340</v>
       </c>
       <c r="N128" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B128, $C$2:$C$785, C128, $D$2:$D$785, D128, $E$2:$E$785, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7063,7 +7067,7 @@
       <c r="I129" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J129" s="59" t="s">
+      <c r="J129" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K129" s="18" t="s">
@@ -7073,57 +7077,57 @@
         <v>4080</v>
       </c>
       <c r="M129" s="18">
-        <f>ABS((D129*E129)-L129)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B129, $C$2:$C$785, C129, $D$2:$D$785, D129, $E$2:$E$785, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
     <row r="130" spans="1:16" s="25" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="68">
+      <c r="A130" s="66">
         <v>46265.375694444447</v>
       </c>
-      <c r="B130" s="66" t="s">
+      <c r="B130" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="C130" s="66" t="s">
-        <v>7</v>
-      </c>
-      <c r="D130" s="63">
+      <c r="C130" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130" s="61">
         <v>5</v>
       </c>
-      <c r="E130" s="63">
+      <c r="E130" s="61">
         <v>1236</v>
       </c>
-      <c r="F130" s="63">
+      <c r="F130" s="61">
         <v>4.4095286370000002</v>
       </c>
-      <c r="G130" s="64" t="s">
+      <c r="G130" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="H130" s="65">
+      <c r="H130" s="63">
         <v>1183.8</v>
       </c>
-      <c r="I130" s="66" t="s">
-        <v>8</v>
-      </c>
-      <c r="J130" s="67" t="s">
+      <c r="I130" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="J130" s="65" t="s">
         <v>118</v>
       </c>
-      <c r="K130" s="67" t="s">
+      <c r="K130" s="65" t="s">
         <v>214</v>
       </c>
-      <c r="L130" s="67">
+      <c r="L130" s="65">
         <v>5905</v>
       </c>
-      <c r="M130" s="67">
-        <f>ABS((D130*E130)-L130)</f>
+      <c r="M130" s="65">
+        <f t="shared" si="4"/>
         <v>275</v>
       </c>
-      <c r="N130" s="69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B130, $C$2:$C$785, C130, $D$2:$D$785, D130, $E$2:$E$785, E130) &gt; 1, "Duplicate", "Unique")</f>
+      <c r="N130" s="67" t="str">
+        <f t="shared" ref="N130:N193" si="5">IF(COUNTIFS( $B$2:$B$785, B130, $C$2:$C$785, C130, $D$2:$D$785, D130, $E$2:$E$785, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P130" s="25" t="s">
@@ -7168,11 +7172,11 @@
         <v>15075</v>
       </c>
       <c r="M131" s="18">
-        <f>ABS((D131*E131)-L131)</f>
+        <f t="shared" si="4"/>
         <v>525</v>
       </c>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B131, $C$2:$C$785, C131, $D$2:$D$785, D131, $E$2:$E$785, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7214,11 +7218,11 @@
         <v>26180</v>
       </c>
       <c r="M132" s="18">
-        <f>ABS((D132*E132)-L132)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B132, $C$2:$C$785, C132, $D$2:$D$785, D132, $E$2:$E$785, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7260,16 +7264,14 @@
         <v>32200</v>
       </c>
       <c r="M133" s="18">
-        <f>ABS((D133*E133)-L133)</f>
+        <f t="shared" si="4"/>
         <v>1200</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B133, $C$2:$C$785, C133, $D$2:$D$785, D133, $E$2:$E$785, E133) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O133" s="47" t="s">
-        <v>262</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>Unique</v>
+      </c>
+      <c r="O133" s="74"/>
     </row>
     <row r="134" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="3">
@@ -7309,11 +7311,11 @@
         <v>12600</v>
       </c>
       <c r="M134" s="18">
-        <f>ABS((D134*E134)-L134)</f>
+        <f t="shared" si="4"/>
         <v>360</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B134, $C$2:$C$785, C134, $D$2:$D$785, D134, $E$2:$E$785, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7345,7 +7347,7 @@
       <c r="I135" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J135" s="59" t="s">
+      <c r="J135" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K135" s="18" t="s">
@@ -7355,11 +7357,11 @@
         <v>3005</v>
       </c>
       <c r="M135" s="18">
-        <f>ABS((D135*E135)-L135)</f>
+        <f t="shared" si="4"/>
         <v>240</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B135, $C$2:$C$785, C135, $D$2:$D$785, D135, $E$2:$E$785, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O135" s="10"/>
@@ -7402,11 +7404,11 @@
         <v>26300</v>
       </c>
       <c r="M136" s="18">
-        <f>ABS((D136*E136)-L136)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B136, $C$2:$C$785, C136, $D$2:$D$785, D136, $E$2:$E$785, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7440,7 +7442,7 @@
       </c>
       <c r="J137" s="40"/>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B137, $C$2:$C$785, C137, $D$2:$D$785, D137, $E$2:$E$785, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="25"/>
@@ -7487,7 +7489,7 @@
         <v>300</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B138, $C$2:$C$785, C138, $D$2:$D$785, D138, $E$2:$E$785, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O138" s="10"/>
@@ -7534,7 +7536,7 @@
         <v>300</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B139, $C$2:$C$785, C139, $D$2:$D$785, D139, $E$2:$E$785, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O139" s="47" t="s">
@@ -7583,7 +7585,7 @@
         <v>300</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B140, $C$2:$C$785, C140, $D$2:$D$785, D140, $E$2:$E$785, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O140"/>
@@ -7620,7 +7622,7 @@
         <v>118</v>
       </c>
       <c r="N141" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B141, $C$2:$C$785, C141, $D$2:$D$785, D141, $E$2:$E$785, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O141" s="47" t="s">
@@ -7664,7 +7666,7 @@
       <c r="L142" s="17"/>
       <c r="M142" s="17"/>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B142, $C$2:$C$785, C142, $D$2:$D$785, D142, $E$2:$E$785, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7710,7 +7712,7 @@
         <v>150</v>
       </c>
       <c r="N143" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B143, $C$2:$C$785, C143, $D$2:$D$785, D143, $E$2:$E$785, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -7756,7 +7758,7 @@
         <v>250</v>
       </c>
       <c r="N144" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B144, $C$2:$C$785, C144, $D$2:$D$785, D144, $E$2:$E$785, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -7802,7 +7804,7 @@
         <v>300</v>
       </c>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B145, $C$2:$C$785, C145, $D$2:$D$785, D145, $E$2:$E$785, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7848,7 +7850,7 @@
         <v>500</v>
       </c>
       <c r="N146" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B146, $C$2:$C$785, C146, $D$2:$D$785, D146, $E$2:$E$785, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O146" s="48" t="s">
@@ -7885,7 +7887,7 @@
       </c>
       <c r="J147" s="40"/>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B147, $C$2:$C$785, C147, $D$2:$D$785, D147, $E$2:$E$785, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7931,7 +7933,7 @@
         <v>270</v>
       </c>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B148, $C$2:$C$785, C148, $D$2:$D$785, D148, $E$2:$E$785, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O148" s="48" t="s">
@@ -7980,46 +7982,46 @@
         <v>300</v>
       </c>
       <c r="N149" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B149, $C$2:$C$785, C149, $D$2:$D$785, D149, $E$2:$E$785, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
     <row r="150" spans="1:16" s="25" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="62" t="s">
+      <c r="A150" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="B150" s="70" t="s">
+      <c r="B150" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="C150" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="D150" s="62">
+      <c r="C150" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="D150" s="60">
         <v>40</v>
       </c>
-      <c r="E150" s="71">
+      <c r="E150" s="69">
         <v>229</v>
       </c>
-      <c r="F150" s="63">
+      <c r="F150" s="61">
         <v>6.0185185189999997</v>
       </c>
-      <c r="G150" s="64" t="s">
+      <c r="G150" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="H150" s="65">
+      <c r="H150" s="63">
         <v>216</v>
       </c>
-      <c r="I150" s="66" t="s">
-        <v>8</v>
-      </c>
-      <c r="J150" s="72" t="s">
+      <c r="I150" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="J150" s="70" t="s">
         <v>117</v>
       </c>
-      <c r="K150" s="67"/>
-      <c r="L150" s="67"/>
-      <c r="M150" s="67"/>
+      <c r="K150" s="65"/>
+      <c r="L150" s="65"/>
+      <c r="M150" s="65"/>
       <c r="N150" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B150, $C$2:$C$785, C150, $D$2:$D$785, D150, $E$2:$E$785, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P150" s="25" t="s">
@@ -8068,7 +8070,7 @@
         <v>300</v>
       </c>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B151, $C$2:$C$785, C151, $D$2:$D$785, D151, $E$2:$E$785, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O151" s="35"/>
@@ -8115,7 +8117,7 @@
         <v>1000</v>
       </c>
       <c r="N152" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B152, $C$2:$C$785, C152, $D$2:$D$785, D152, $E$2:$E$785, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O152" s="26"/>
@@ -8162,7 +8164,7 @@
         <v>700</v>
       </c>
       <c r="N153" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B153, $C$2:$C$785, C153, $D$2:$D$785, D153, $E$2:$E$785, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -8208,7 +8210,7 @@
         <v>250</v>
       </c>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B154, $C$2:$C$785, C154, $D$2:$D$785, D154, $E$2:$E$785, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8254,7 +8256,7 @@
         <v>300</v>
       </c>
       <c r="N155" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B155, $C$2:$C$785, C155, $D$2:$D$785, D155, $E$2:$E$785, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8290,11 +8292,11 @@
         <v>156</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B156, $C$2:$C$785, C156, $D$2:$D$785, D156, $E$2:$E$785, E156) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="157" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="11">
         <v>46243.375</v>
       </c>
@@ -8336,8 +8338,11 @@
         <v>650</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B157, $C$2:$C$785, C157, $D$2:$D$785, D157, $E$2:$E$785, E157) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
+        <f t="shared" si="5"/>
+        <v>Unique</v>
+      </c>
+      <c r="O157" s="47" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="158" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8382,7 +8387,7 @@
         <v>268</v>
       </c>
       <c r="N158" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B158, $C$2:$C$785, C158, $D$2:$D$785, D158, $E$2:$E$785, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O158" s="47" t="s">
@@ -8431,7 +8436,7 @@
         <v>400</v>
       </c>
       <c r="N159" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B159, $C$2:$C$785, C159, $D$2:$D$785, D159, $E$2:$E$785, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8477,7 +8482,7 @@
         <v>295</v>
       </c>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B160, $C$2:$C$785, C160, $D$2:$D$785, D160, $E$2:$E$785, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8511,7 +8516,7 @@
       </c>
       <c r="J161" s="40"/>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B161, $C$2:$C$785, C161, $D$2:$D$785, D161, $E$2:$E$785, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8547,7 +8552,7 @@
         <v>118</v>
       </c>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B162, $C$2:$C$785, C162, $D$2:$D$785, D162, $E$2:$E$785, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8583,7 +8588,7 @@
         <v>117</v>
       </c>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B163, $C$2:$C$785, C163, $D$2:$D$785, D163, $E$2:$E$785, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8629,7 +8634,7 @@
         <v>300</v>
       </c>
       <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B164, $C$2:$C$785, C164, $D$2:$D$785, D164, $E$2:$E$785, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8675,7 +8680,7 @@
         <v>294</v>
       </c>
       <c r="N165" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B165, $C$2:$C$785, C165, $D$2:$D$785, D165, $E$2:$E$785, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -8721,7 +8726,7 @@
         <v>294</v>
       </c>
       <c r="N166" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B166, $C$2:$C$785, C166, $D$2:$D$785, D166, $E$2:$E$785, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -8767,7 +8772,7 @@
         <v>280</v>
       </c>
       <c r="N167" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B167, $C$2:$C$785, C167, $D$2:$D$785, D167, $E$2:$E$785, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8813,7 +8818,7 @@
         <v>300</v>
       </c>
       <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B168, $C$2:$C$785, C168, $D$2:$D$785, D168, $E$2:$E$785, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8847,7 +8852,7 @@
       </c>
       <c r="J169" s="40"/>
       <c r="N169" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B169, $C$2:$C$785, C169, $D$2:$D$785, D169, $E$2:$E$785, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8893,7 +8898,7 @@
         <v>250</v>
       </c>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B170, $C$2:$C$785, C170, $D$2:$D$785, D170, $E$2:$E$785, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O170" s="10"/>
@@ -8940,7 +8945,7 @@
         <v>260</v>
       </c>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B171, $C$2:$C$785, C171, $D$2:$D$785, D171, $E$2:$E$785, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8986,7 +8991,7 @@
         <v>500</v>
       </c>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B172, $C$2:$C$785, C172, $D$2:$D$785, D172, $E$2:$E$785, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9022,7 +9027,7 @@
         <v>117</v>
       </c>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B173, $C$2:$C$785, C173, $D$2:$D$785, D173, $E$2:$E$785, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9056,7 +9061,7 @@
       </c>
       <c r="J174" s="40"/>
       <c r="N174" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B174, $C$2:$C$785, C174, $D$2:$D$785, D174, $E$2:$E$785, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9102,7 +9107,7 @@
         <v>370</v>
       </c>
       <c r="N175" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B175, $C$2:$C$785, C175, $D$2:$D$785, D175, $E$2:$E$785, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O175" s="10"/>
@@ -9149,7 +9154,7 @@
         <v>320</v>
       </c>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B176, $C$2:$C$785, C176, $D$2:$D$785, D176, $E$2:$E$785, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9195,7 +9200,7 @@
         <v>448</v>
       </c>
       <c r="N177" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B177, $C$2:$C$785, C177, $D$2:$D$785, D177, $E$2:$E$785, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9231,7 +9236,7 @@
         <v>201</v>
       </c>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B178, $C$2:$C$785, C178, $D$2:$D$785, D178, $E$2:$E$785, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9273,15 +9278,15 @@
         <v>5290</v>
       </c>
       <c r="M179" s="18">
-        <f>ABS((D179*E179)-L179)</f>
+        <f t="shared" ref="M179:M187" si="6">ABS((D179*E179)-L179)</f>
         <v>250</v>
       </c>
       <c r="N179" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B179, $C$2:$C$785, C179, $D$2:$D$785, D179, $E$2:$E$785, E179) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="180" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="3">
         <v>46269.411111111112</v>
       </c>
@@ -9319,11 +9324,11 @@
         <v>18140</v>
       </c>
       <c r="M180" s="27">
-        <f>ABS((D180*E180)-L180)</f>
+        <f t="shared" si="6"/>
         <v>650</v>
       </c>
       <c r="N180" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B180, $C$2:$C$785, C180, $D$2:$D$785, D180, $E$2:$E$785, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="47" t="s">
@@ -9368,11 +9373,11 @@
         <v>17040</v>
       </c>
       <c r="M181" s="18">
-        <f>ABS((D181*E181)-L181)</f>
+        <f t="shared" si="6"/>
         <v>880</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B181, $C$2:$C$785, C181, $D$2:$D$785, D181, $E$2:$E$785, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9414,11 +9419,11 @@
         <v>5520</v>
       </c>
       <c r="M182" s="33">
-        <f>ABS((D182*E182)-L182)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N182" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B182, $C$2:$C$785, C182, $D$2:$D$785, D182, $E$2:$E$785, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O182" s="35"/>
@@ -9461,11 +9466,11 @@
         <v>2657</v>
       </c>
       <c r="M183" s="33">
-        <f>ABS((D183*E183)-L183)</f>
+        <f t="shared" si="6"/>
         <v>253</v>
       </c>
       <c r="N183" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B183, $C$2:$C$785, C183, $D$2:$D$785, D183, $E$2:$E$785, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O183" s="35"/>
@@ -9508,11 +9513,11 @@
         <v>3810</v>
       </c>
       <c r="M184" s="18">
-        <f>ABS((D184*E184)-L184)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N184" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B184, $C$2:$C$785, C184, $D$2:$D$785, D184, $E$2:$E$785, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9554,11 +9559,11 @@
         <v>9312.5</v>
       </c>
       <c r="M185" s="18">
-        <f>ABS((D185*E185)-L185)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B185, $C$2:$C$785, C185, $D$2:$D$785, D185, $E$2:$E$785, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O185" s="47" t="s">
@@ -9603,11 +9608,11 @@
         <v>4680</v>
       </c>
       <c r="M186" s="33">
-        <f>ABS((D186*E186)-L186)</f>
+        <f t="shared" si="6"/>
         <v>140</v>
       </c>
       <c r="N186" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B186, $C$2:$C$785, C186, $D$2:$D$785, D186, $E$2:$E$785, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O186" s="10"/>
@@ -9650,11 +9655,11 @@
         <v>4520</v>
       </c>
       <c r="M187" s="33">
-        <f>ABS((D187*E187)-L187)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N187" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B187, $C$2:$C$785, C187, $D$2:$D$785, D187, $E$2:$E$785, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -9688,7 +9693,7 @@
       </c>
       <c r="J188" s="40"/>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B188, $C$2:$C$785, C188, $D$2:$D$785, D188, $E$2:$E$785, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O188" s="35"/>
@@ -9725,7 +9730,7 @@
         <v>118</v>
       </c>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B189, $C$2:$C$785, C189, $D$2:$D$785, D189, $E$2:$E$785, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O189" s="47" t="s">
@@ -9764,7 +9769,7 @@
         <v>117</v>
       </c>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B190, $C$2:$C$785, C190, $D$2:$D$785, D190, $E$2:$E$785, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9810,7 +9815,7 @@
         <v>700</v>
       </c>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B191, $C$2:$C$785, C191, $D$2:$D$785, D191, $E$2:$E$785, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O191" s="35"/>
@@ -9857,7 +9862,7 @@
         <v>501</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B192, $C$2:$C$785, C192, $D$2:$D$785, D192, $E$2:$E$785, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O192" s="47" t="s">
@@ -9896,7 +9901,7 @@
         <v>118</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B193, $C$2:$C$785, C193, $D$2:$D$785, D193, $E$2:$E$785, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9942,7 +9947,7 @@
         <v>300</v>
       </c>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B194, $C$2:$C$785, C194, $D$2:$D$785, D194, $E$2:$E$785, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="7">IF(COUNTIFS( $B$2:$B$785, B194, $C$2:$C$785, C194, $D$2:$D$785, D194, $E$2:$E$785, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -9976,7 +9981,7 @@
       </c>
       <c r="J195" s="40"/>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B195, $C$2:$C$785, C195, $D$2:$D$785, D195, $E$2:$E$785, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10010,11 +10015,11 @@
       </c>
       <c r="J196" s="40"/>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B196, $C$2:$C$785, C196, $D$2:$D$785, D196, $E$2:$E$785, E196) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="197" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="3">
         <v>46272.451388888891</v>
       </c>
@@ -10056,11 +10061,11 @@
         <v>650</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B197, $C$2:$C$785, C197, $D$2:$D$785, D197, $E$2:$E$785, E197) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="198" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="3">
         <v>46272.390972222223</v>
       </c>
@@ -10102,7 +10107,7 @@
         <v>934</v>
       </c>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B198, $C$2:$C$785, C198, $D$2:$D$785, D198, $E$2:$E$785, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10136,7 +10141,7 @@
       </c>
       <c r="J199" s="40"/>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B199, $C$2:$C$785, C199, $D$2:$D$785, D199, $E$2:$E$785, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10182,7 +10187,7 @@
         <v>1800</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B200, $C$2:$C$785, C200, $D$2:$D$785, D200, $E$2:$E$785, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10228,24 +10233,24 @@
         <v>527.5</v>
       </c>
       <c r="N201" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B201, $C$2:$C$785, C201, $D$2:$D$785, D201, $E$2:$E$785, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
     <row r="202" spans="1:15" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="73">
+      <c r="A202" s="71">
         <v>46253.4</v>
       </c>
-      <c r="B202" s="74" t="s">
+      <c r="B202" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="C202" s="74" t="s">
-        <v>7</v>
-      </c>
-      <c r="D202" s="74">
+      <c r="C202" s="72" t="s">
+        <v>7</v>
+      </c>
+      <c r="D202" s="72">
         <v>30</v>
       </c>
-      <c r="E202" s="74">
+      <c r="E202" s="72">
         <v>294</v>
       </c>
       <c r="F202" s="54">
@@ -10260,7 +10265,7 @@
       <c r="I202" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="J202" s="75" t="s">
+      <c r="J202" s="73" t="s">
         <v>118</v>
       </c>
       <c r="K202" s="33" t="s">
@@ -10269,7 +10274,7 @@
       <c r="L202" s="33"/>
       <c r="M202" s="33"/>
       <c r="N202" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B202, $C$2:$C$785, C202, $D$2:$D$785, D202, $E$2:$E$785, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10315,7 +10320,7 @@
         <v>260</v>
       </c>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B203, $C$2:$C$785, C203, $D$2:$D$785, D203, $E$2:$E$785, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10351,7 +10356,7 @@
         <v>117</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B204, $C$2:$C$785, C204, $D$2:$D$785, D204, $E$2:$E$785, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10387,7 +10392,7 @@
         <v>117</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B205, $C$2:$C$785, C205, $D$2:$D$785, D205, $E$2:$E$785, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10419,7 +10424,7 @@
       <c r="I206" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J206" s="59" t="s">
+      <c r="J206" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K206" s="18" t="s">
@@ -10433,7 +10438,7 @@
         <v>300</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B206, $C$2:$C$785, C206, $D$2:$D$785, D206, $E$2:$E$785, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10470,7 +10475,7 @@
       <c r="L207" s="18"/>
       <c r="M207" s="18"/>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B207, $C$2:$C$785, C207, $D$2:$D$785, D207, $E$2:$E$785, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O207" s="10"/>
@@ -10510,7 +10515,7 @@
         <v>144</v>
       </c>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B208, $C$2:$C$785, C208, $D$2:$D$785, D208, $E$2:$E$785, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10544,7 +10549,7 @@
       </c>
       <c r="J209" s="40"/>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B209, $C$2:$C$785, C209, $D$2:$D$785, D209, $E$2:$E$785, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10578,7 +10583,7 @@
       </c>
       <c r="J210" s="40"/>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B210, $C$2:$C$785, C210, $D$2:$D$785, D210, $E$2:$E$785, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10614,7 +10619,7 @@
         <v>118</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B211, $C$2:$C$785, C211, $D$2:$D$785, D211, $E$2:$E$785, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O211" s="35"/>
@@ -10654,7 +10659,7 @@
         <v>145</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B212, $C$2:$C$785, C212, $D$2:$D$785, D212, $E$2:$E$785, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10688,7 +10693,7 @@
       </c>
       <c r="J213" s="40"/>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B213, $C$2:$C$785, C213, $D$2:$D$785, D213, $E$2:$E$785, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10734,7 +10739,7 @@
         <v>300</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B214, $C$2:$C$785, C214, $D$2:$D$785, D214, $E$2:$E$785, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10780,7 +10785,7 @@
         <v>188</v>
       </c>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B215, $C$2:$C$785, C215, $D$2:$D$785, D215, $E$2:$E$785, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O215" s="10"/>
@@ -10817,7 +10822,7 @@
         <v>55</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B216, $C$2:$C$785, C216, $D$2:$D$785, D216, $E$2:$E$785, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10853,7 +10858,7 @@
         <v>118</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B217, $C$2:$C$785, C217, $D$2:$D$785, D217, $E$2:$E$785, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10889,7 +10894,7 @@
         <v>118</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B218, $C$2:$C$785, C218, $D$2:$D$785, D218, $E$2:$E$785, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10925,11 +10930,11 @@
         <v>117</v>
       </c>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B219, $C$2:$C$785, C219, $D$2:$D$785, D219, $E$2:$E$785, E219) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="220" spans="1:15" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="3">
         <v>46260.425694444442</v>
       </c>
@@ -10971,12 +10976,10 @@
         <v>1000</v>
       </c>
       <c r="N220" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B220, $C$2:$C$785, C220, $D$2:$D$785, D220, $E$2:$E$785, E220) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O220" s="47" t="s">
-        <v>262</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+      <c r="O220" s="74"/>
     </row>
     <row r="221" spans="1:15" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="8" t="s">
@@ -11013,7 +11016,7 @@
       <c r="L221" s="18"/>
       <c r="M221" s="18"/>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B221, $C$2:$C$785, C221, $D$2:$D$785, D221, $E$2:$E$785, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O221" s="10"/>
@@ -11050,7 +11053,7 @@
         <v>117</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B222, $C$2:$C$785, C222, $D$2:$D$785, D222, $E$2:$E$785, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11084,7 +11087,7 @@
       </c>
       <c r="J223" s="40"/>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B223, $C$2:$C$785, C223, $D$2:$D$785, D223, $E$2:$E$785, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O223" s="35"/>
@@ -11121,7 +11124,7 @@
         <v>117</v>
       </c>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B224, $C$2:$C$785, C224, $D$2:$D$785, D224, $E$2:$E$785, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11155,7 +11158,7 @@
       </c>
       <c r="J225" s="40"/>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B225, $C$2:$C$785, C225, $D$2:$D$785, D225, $E$2:$E$785, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11191,7 +11194,7 @@
         <v>118</v>
       </c>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B226, $C$2:$C$785, C226, $D$2:$D$785, D226, $E$2:$E$785, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11227,7 +11230,7 @@
         <v>118</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B227, $C$2:$C$785, C227, $D$2:$D$785, D227, $E$2:$E$785, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11273,7 +11276,7 @@
         <v>300</v>
       </c>
       <c r="N228" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B228, $C$2:$C$785, C228, $D$2:$D$785, D228, $E$2:$E$785, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11319,11 +11322,11 @@
         <v>250</v>
       </c>
       <c r="N229" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B229, $C$2:$C$785, C229, $D$2:$D$785, D229, $E$2:$E$785, E229) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="230" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="3">
         <v>46259.388194444444</v>
       </c>
@@ -11365,7 +11368,7 @@
         <v>940</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B230, $C$2:$C$785, C230, $D$2:$D$785, D230, $E$2:$E$785, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11411,7 +11414,7 @@
         <v>285</v>
       </c>
       <c r="N231" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B231, $C$2:$C$785, C231, $D$2:$D$785, D231, $E$2:$E$785, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11457,7 +11460,7 @@
         <v>726</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B232, $C$2:$C$785, C232, $D$2:$D$785, D232, $E$2:$E$785, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11491,7 +11494,7 @@
       </c>
       <c r="J233" s="40"/>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B233, $C$2:$C$785, C233, $D$2:$D$785, D233, $E$2:$E$785, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11527,7 +11530,7 @@
         <v>55</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B234, $C$2:$C$785, C234, $D$2:$D$785, D234, $E$2:$E$785, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11573,7 +11576,7 @@
         <v>300</v>
       </c>
       <c r="N235" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B235, $C$2:$C$785, C235, $D$2:$D$785, D235, $E$2:$E$785, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11609,7 +11612,7 @@
         <v>118</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B236, $C$2:$C$785, C236, $D$2:$D$785, D236, $E$2:$E$785, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11655,7 +11658,7 @@
         <v>800</v>
       </c>
       <c r="N237" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B237, $C$2:$C$785, C237, $D$2:$D$785, D237, $E$2:$E$785, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11691,7 +11694,7 @@
         <v>118</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B238, $C$2:$C$785, C238, $D$2:$D$785, D238, $E$2:$E$785, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11737,7 +11740,7 @@
         <v>650</v>
       </c>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B239, $C$2:$C$785, C239, $D$2:$D$785, D239, $E$2:$E$785, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O239" s="35"/>
@@ -11784,7 +11787,7 @@
         <v>275</v>
       </c>
       <c r="N240" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B240, $C$2:$C$785, C240, $D$2:$D$785, D240, $E$2:$E$785, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11823,7 +11826,7 @@
         <v>146</v>
       </c>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B241, $C$2:$C$785, C241, $D$2:$D$785, D241, $E$2:$E$785, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11869,11 +11872,11 @@
         <v>480</v>
       </c>
       <c r="N242" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B242, $C$2:$C$785, C242, $D$2:$D$785, D242, $E$2:$E$785, E242) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="243" spans="1:15" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="3">
         <v>46260.375</v>
       </c>
@@ -11915,7 +11918,7 @@
         <v>650</v>
       </c>
       <c r="N243" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B243, $C$2:$C$785, C243, $D$2:$D$785, D243, $E$2:$E$785, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O243" s="10"/>
@@ -11950,7 +11953,7 @@
       </c>
       <c r="J244" s="40"/>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B244, $C$2:$C$785, C244, $D$2:$D$785, D244, $E$2:$E$785, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11984,7 +11987,7 @@
       </c>
       <c r="J245" s="40"/>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B245, $C$2:$C$785, C245, $D$2:$D$785, D245, $E$2:$E$785, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12018,7 +12021,7 @@
       </c>
       <c r="J246" s="40"/>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B246, $C$2:$C$785, C246, $D$2:$D$785, D246, $E$2:$E$785, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12052,7 +12055,7 @@
       </c>
       <c r="J247" s="40"/>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B247, $C$2:$C$785, C247, $D$2:$D$785, D247, $E$2:$E$785, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12098,7 +12101,7 @@
         <v>250</v>
       </c>
       <c r="N248" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B248, $C$2:$C$785, C248, $D$2:$D$785, D248, $E$2:$E$785, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O248" s="10"/>
@@ -12135,7 +12138,7 @@
         <v>118</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B249, $C$2:$C$785, C249, $D$2:$D$785, D249, $E$2:$E$785, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12169,7 +12172,7 @@
       </c>
       <c r="J250" s="40"/>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B250, $C$2:$C$785, C250, $D$2:$D$785, D250, $E$2:$E$785, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12203,11 +12206,11 @@
       </c>
       <c r="J251" s="40"/>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B251, $C$2:$C$785, C251, $D$2:$D$785, D251, $E$2:$E$785, E251) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="252" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="252" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="11">
         <v>46252.6875</v>
       </c>
@@ -12239,7 +12242,7 @@
         <v>118</v>
       </c>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B252, $C$2:$C$785, C252, $D$2:$D$785, D252, $E$2:$E$785, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O252" s="35"/>
@@ -12286,7 +12289,7 @@
         <v>300</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B253, $C$2:$C$785, C253, $D$2:$D$785, D253, $E$2:$E$785, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12320,7 +12323,7 @@
       </c>
       <c r="J254" s="40"/>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B254, $C$2:$C$785, C254, $D$2:$D$785, D254, $E$2:$E$785, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12354,7 +12357,7 @@
       </c>
       <c r="J255" s="40"/>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B255, $C$2:$C$785, C255, $D$2:$D$785, D255, $E$2:$E$785, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12390,7 +12393,7 @@
         <v>118</v>
       </c>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B256, $C$2:$C$785, C256, $D$2:$D$785, D256, $E$2:$E$785, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O256" s="35"/>
@@ -12425,7 +12428,7 @@
       </c>
       <c r="J257" s="40"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B257, $C$2:$C$785, C257, $D$2:$D$785, D257, $E$2:$E$785, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12459,7 +12462,7 @@
       </c>
       <c r="J258" s="40"/>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B258, $C$2:$C$785, C258, $D$2:$D$785, D258, $E$2:$E$785, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N282" si="8">IF(COUNTIFS( $B$2:$B$785, B258, $C$2:$C$785, C258, $D$2:$D$785, D258, $E$2:$E$785, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12493,7 +12496,7 @@
       </c>
       <c r="J259" s="40"/>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B259, $C$2:$C$785, C259, $D$2:$D$785, D259, $E$2:$E$785, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12529,7 +12532,7 @@
         <v>117</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B260, $C$2:$C$785, C260, $D$2:$D$785, D260, $E$2:$E$785, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12565,7 +12568,7 @@
         <v>118</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B261, $C$2:$C$785, C261, $D$2:$D$785, D261, $E$2:$E$785, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12599,7 +12602,7 @@
       </c>
       <c r="J262" s="40"/>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B262, $C$2:$C$785, C262, $D$2:$D$785, D262, $E$2:$E$785, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12633,7 +12636,7 @@
       </c>
       <c r="J263" s="40"/>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B263, $C$2:$C$785, C263, $D$2:$D$785, D263, $E$2:$E$785, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12667,7 +12670,7 @@
       </c>
       <c r="J264" s="40"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B264, $C$2:$C$785, C264, $D$2:$D$785, D264, $E$2:$E$785, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O264" s="35"/>
@@ -12702,7 +12705,7 @@
       </c>
       <c r="J265" s="40"/>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B265, $C$2:$C$785, C265, $D$2:$D$785, D265, $E$2:$E$785, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12736,7 +12739,7 @@
       </c>
       <c r="J266" s="40"/>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B266, $C$2:$C$785, C266, $D$2:$D$785, D266, $E$2:$E$785, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12773,7 +12776,7 @@
       <c r="L267" s="18"/>
       <c r="M267" s="18"/>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B267, $C$2:$C$785, C267, $D$2:$D$785, D267, $E$2:$E$785, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O267" s="10"/>
@@ -12810,7 +12813,7 @@
         <v>55</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B268, $C$2:$C$785, C268, $D$2:$D$785, D268, $E$2:$E$785, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12856,7 +12859,7 @@
         <v>250</v>
       </c>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B269, $C$2:$C$785, C269, $D$2:$D$785, D269, $E$2:$E$785, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12890,7 +12893,7 @@
       </c>
       <c r="J270" s="40"/>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B270, $C$2:$C$785, C270, $D$2:$D$785, D270, $E$2:$E$785, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12924,7 +12927,7 @@
       </c>
       <c r="J271" s="40"/>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B271, $C$2:$C$785, C271, $D$2:$D$785, D271, $E$2:$E$785, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12960,7 +12963,7 @@
         <v>118</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B272, $C$2:$C$785, C272, $D$2:$D$785, D272, $E$2:$E$785, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12996,11 +12999,11 @@
         <v>118</v>
       </c>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B273, $C$2:$C$785, C273, $D$2:$D$785, D273, $E$2:$E$785, E273) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="274" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="8"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="274" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="11">
         <v>46252.6875</v>
       </c>
@@ -13032,7 +13035,7 @@
         <v>118</v>
       </c>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B274, $C$2:$C$785, C274, $D$2:$D$785, D274, $E$2:$E$785, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13066,11 +13069,11 @@
       </c>
       <c r="J275" s="40"/>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B275, $C$2:$C$785, C275, $D$2:$D$785, D275, $E$2:$E$785, E275) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="276" spans="1:15" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="8"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="276" spans="1:15" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="8" t="s">
         <v>62</v>
       </c>
@@ -13103,12 +13106,12 @@
       <c r="L276" s="18"/>
       <c r="M276" s="18"/>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B276, $C$2:$C$785, C276, $D$2:$D$785, D276, $E$2:$E$785, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O276" s="10"/>
     </row>
-    <row r="277" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="8" t="s">
         <v>62</v>
       </c>
@@ -13138,7 +13141,7 @@
       </c>
       <c r="J277" s="40"/>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B277, $C$2:$C$785, C277, $D$2:$D$785, D277, $E$2:$E$785, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13184,11 +13187,11 @@
         <v>250</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B278, $C$2:$C$785, C278, $D$2:$D$785, D278, $E$2:$E$785, E278) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="279" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="8"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="279" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="8" t="s">
         <v>62</v>
       </c>
@@ -13218,11 +13221,11 @@
       </c>
       <c r="J279" s="40"/>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B279, $C$2:$C$785, C279, $D$2:$D$785, D279, $E$2:$E$785, E279) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="280" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="8"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="280" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="8" t="s">
         <v>62</v>
       </c>
@@ -13252,11 +13255,11 @@
       </c>
       <c r="J280" s="40"/>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B280, $C$2:$C$785, C280, $D$2:$D$785, D280, $E$2:$E$785, E280) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="281" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="8"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="281" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="11">
         <v>46251.506249999999</v>
       </c>
@@ -13286,7 +13289,7 @@
       </c>
       <c r="J281" s="40"/>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B281, $C$2:$C$785, C281, $D$2:$D$785, D281, $E$2:$E$785, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O281" s="35"/>
@@ -13321,20 +13324,17 @@
       </c>
       <c r="J282" s="40"/>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$785, B282, $C$2:$C$785, C282, $D$2:$D$785, D282, $E$2:$E$785, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P282" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
+    <filterColumn colId="1">
       <filters>
-        <filter val="B"/>
+        <filter val="KERNEXEQ"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P97">
-      <sortCondition descending="1" ref="F1:F282"/>
-    </sortState>
   </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13834,7 +13834,7 @@
         <v>200</v>
       </c>
       <c r="N2" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B2, $C$2:$C$786, C2, $D$2:$D$786, D2, $E$2:$E$786, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$786, B2, $C$2:$C$786, C2, $D$2:$D$786, D2, $E$2:$E$786, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O2" s="10"/>
@@ -13881,7 +13881,7 @@
         <v>300</v>
       </c>
       <c r="N3" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B3, $C$2:$C$786, C3, $D$2:$D$786, D3, $E$2:$E$786, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O3" s="10"/>
@@ -13919,7 +13919,7 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B4, $C$2:$C$786, C4, $D$2:$D$786, D4, $E$2:$E$786, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
@@ -13959,7 +13959,7 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B5, $C$2:$C$786, C5, $D$2:$D$786, D5, $E$2:$E$786, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -13999,7 +13999,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B6, $C$2:$C$786, C6, $D$2:$D$786, D6, $E$2:$E$786, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="10"/>
@@ -14037,7 +14037,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B7, $C$2:$C$786, C7, $D$2:$D$786, D7, $E$2:$E$786, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="10"/>
@@ -14075,7 +14075,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B8, $C$2:$C$786, C8, $D$2:$D$786, D8, $E$2:$E$786, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="10"/>
@@ -14113,7 +14113,7 @@
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B9, $C$2:$C$786, C9, $D$2:$D$786, D9, $E$2:$E$786, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="10"/>
@@ -14151,7 +14151,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B10, $C$2:$C$786, C10, $D$2:$D$786, D10, $E$2:$E$786, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="10"/>
@@ -14189,7 +14189,7 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B11, $C$2:$C$786, C11, $D$2:$D$786, D11, $E$2:$E$786, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="26"/>
@@ -14236,7 +14236,7 @@
         <v>300</v>
       </c>
       <c r="N12" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B12, $C$2:$C$786, C12, $D$2:$D$786, D12, $E$2:$E$786, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="25"/>
@@ -14283,7 +14283,7 @@
         <v>500</v>
       </c>
       <c r="N13" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B13, $C$2:$C$786, C13, $D$2:$D$786, D13, $E$2:$E$786, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="10"/>
@@ -14323,7 +14323,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B14, $C$2:$C$786, C14, $D$2:$D$786, D14, $E$2:$E$786, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14" s="10"/>
@@ -14370,7 +14370,7 @@
         <v>250</v>
       </c>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B15, $C$2:$C$786, C15, $D$2:$D$786, D15, $E$2:$E$786, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O15" s="10"/>
@@ -14408,7 +14408,7 @@
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B16, $C$2:$C$786, C16, $D$2:$D$786, D16, $E$2:$E$786, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16" s="10"/>
@@ -14446,7 +14446,7 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B17, $C$2:$C$786, C17, $D$2:$D$786, D17, $E$2:$E$786, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17" s="19"/>
@@ -14493,7 +14493,7 @@
         <v>450</v>
       </c>
       <c r="N18" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B18, $C$2:$C$786, C18, $D$2:$D$786, D18, $E$2:$E$786, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18" s="10"/>
@@ -14531,7 +14531,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B19, $C$2:$C$786, C19, $D$2:$D$786, D19, $E$2:$E$786, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19" s="10"/>
@@ -14569,7 +14569,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B20, $C$2:$C$786, C20, $D$2:$D$786, D20, $E$2:$E$786, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20" s="10"/>
@@ -14607,7 +14607,7 @@
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B21, $C$2:$C$786, C21, $D$2:$D$786, D21, $E$2:$E$786, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21" s="10"/>
@@ -14654,7 +14654,7 @@
         <v>516</v>
       </c>
       <c r="N22" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B22, $C$2:$C$786, C22, $D$2:$D$786, D22, $E$2:$E$786, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22" s="10"/>
@@ -14701,7 +14701,7 @@
         <v>300</v>
       </c>
       <c r="N23" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B23, $C$2:$C$786, C23, $D$2:$D$786, D23, $E$2:$E$786, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23" s="10"/>
@@ -14739,7 +14739,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B24, $C$2:$C$786, C24, $D$2:$D$786, D24, $E$2:$E$786, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24" s="10"/>
@@ -14779,7 +14779,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B25, $C$2:$C$786, C25, $D$2:$D$786, D25, $E$2:$E$786, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25" s="10"/>
@@ -14819,7 +14819,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B26, $C$2:$C$786, C26, $D$2:$D$786, D26, $E$2:$E$786, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26" s="10"/>
@@ -14857,7 +14857,7 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B27, $C$2:$C$786, C27, $D$2:$D$786, D27, $E$2:$E$786, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27" s="10"/>
@@ -14904,7 +14904,7 @@
         <v>300</v>
       </c>
       <c r="N28" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B28, $C$2:$C$786, C28, $D$2:$D$786, D28, $E$2:$E$786, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28" s="10"/>
@@ -14942,7 +14942,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B29, $C$2:$C$786, C29, $D$2:$D$786, D29, $E$2:$E$786, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29" s="10"/>
@@ -14982,7 +14982,7 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B30, $C$2:$C$786, C30, $D$2:$D$786, D30, $E$2:$E$786, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30" s="10"/>
@@ -15020,7 +15020,7 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B31, $C$2:$C$786, C31, $D$2:$D$786, D31, $E$2:$E$786, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31" s="10"/>
@@ -15058,7 +15058,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B32, $C$2:$C$786, C32, $D$2:$D$786, D32, $E$2:$E$786, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32" s="10"/>
@@ -15096,7 +15096,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B33, $C$2:$C$786, C33, $D$2:$D$786, D33, $E$2:$E$786, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33" s="10"/>
@@ -15136,7 +15136,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B34, $C$2:$C$786, C34, $D$2:$D$786, D34, $E$2:$E$786, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34" s="10"/>
@@ -15174,7 +15174,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B35, $C$2:$C$786, C35, $D$2:$D$786, D35, $E$2:$E$786, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35" s="10"/>
@@ -15217,7 +15217,7 @@
         <v>3156</v>
       </c>
       <c r="N36" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B36, $C$2:$C$786, C36, $D$2:$D$786, D36, $E$2:$E$786, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36" s="10"/>
@@ -15255,7 +15255,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B37, $C$2:$C$786, C37, $D$2:$D$786, D37, $E$2:$E$786, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37" s="25"/>
@@ -15302,7 +15302,7 @@
         <v>300</v>
       </c>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B38, $C$2:$C$786, C38, $D$2:$D$786, D38, $E$2:$E$786, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38" s="10"/>
@@ -15349,7 +15349,7 @@
         <v>300</v>
       </c>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B39, $C$2:$C$786, C39, $D$2:$D$786, D39, $E$2:$E$786, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39" s="10"/>
@@ -15387,7 +15387,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B40, $C$2:$C$786, C40, $D$2:$D$786, D40, $E$2:$E$786, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40" s="10"/>
@@ -15425,7 +15425,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B41, $C$2:$C$786, C41, $D$2:$D$786, D41, $E$2:$E$786, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41" s="10"/>
@@ -15463,7 +15463,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B42, $C$2:$C$786, C42, $D$2:$D$786, D42, $E$2:$E$786, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15500,7 +15500,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B43, $C$2:$C$786, C43, $D$2:$D$786, D43, $E$2:$E$786, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15539,7 +15539,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B44, $C$2:$C$786, C44, $D$2:$D$786, D44, $E$2:$E$786, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44" s="10"/>
@@ -15579,7 +15579,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B45, $C$2:$C$786, C45, $D$2:$D$786, D45, $E$2:$E$786, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15625,7 +15625,7 @@
         <v>222.75</v>
       </c>
       <c r="N46" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B46, $C$2:$C$786, C46, $D$2:$D$786, D46, $E$2:$E$786, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46" s="10"/>
@@ -15665,7 +15665,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B47, $C$2:$C$786, C47, $D$2:$D$786, D47, $E$2:$E$786, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15704,7 +15704,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B48, $C$2:$C$786, C48, $D$2:$D$786, D48, $E$2:$E$786, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15741,7 +15741,7 @@
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
       <c r="N49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B49, $C$2:$C$786, C49, $D$2:$D$786, D49, $E$2:$E$786, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15778,7 +15778,7 @@
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B50, $C$2:$C$786, C50, $D$2:$D$786, D50, $E$2:$E$786, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B51, $C$2:$C$786, C51, $D$2:$D$786, D51, $E$2:$E$786, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15856,7 +15856,7 @@
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B52, $C$2:$C$786, C52, $D$2:$D$786, D52, $E$2:$E$786, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15903,7 +15903,7 @@
         <v>650</v>
       </c>
       <c r="N53" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B53, $C$2:$C$786, C53, $D$2:$D$786, D53, $E$2:$E$786, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15940,7 +15940,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B54, $C$2:$C$786, C54, $D$2:$D$786, D54, $E$2:$E$786, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15977,7 +15977,7 @@
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B55, $C$2:$C$786, C55, $D$2:$D$786, D55, $E$2:$E$786, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -16017,7 +16017,7 @@
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B56, $C$2:$C$786, C56, $D$2:$D$786, D56, $E$2:$E$786, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56"/>
@@ -16064,7 +16064,7 @@
         <v>460</v>
       </c>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B57, $C$2:$C$786, C57, $D$2:$D$786, D57, $E$2:$E$786, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57"/>
@@ -16104,7 +16104,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B58, $C$2:$C$786, C58, $D$2:$D$786, D58, $E$2:$E$786, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58"/>
@@ -16142,7 +16142,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B59, $C$2:$C$786, C59, $D$2:$D$786, D59, $E$2:$E$786, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59" s="34"/>
@@ -16180,7 +16180,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B60, $C$2:$C$786, C60, $D$2:$D$786, D60, $E$2:$E$786, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60"/>
@@ -16220,7 +16220,7 @@
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B61, $C$2:$C$786, C61, $D$2:$D$786, D61, $E$2:$E$786, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61"/>
@@ -16258,7 +16258,7 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B62, $C$2:$C$786, C62, $D$2:$D$786, D62, $E$2:$E$786, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62"/>
@@ -16305,7 +16305,7 @@
         <v>300</v>
       </c>
       <c r="N63" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B63, $C$2:$C$786, C63, $D$2:$D$786, D63, $E$2:$E$786, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63"/>
@@ -16352,7 +16352,7 @@
         <v>300</v>
       </c>
       <c r="N64" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B64, $C$2:$C$786, C64, $D$2:$D$786, D64, $E$2:$E$786, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64"/>
@@ -16390,7 +16390,7 @@
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B65, $C$2:$C$786, C65, $D$2:$D$786, D65, $E$2:$E$786, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O65"/>
@@ -16428,7 +16428,7 @@
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B66, $C$2:$C$786, C66, $D$2:$D$786, D66, $E$2:$E$786, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$786, B66, $C$2:$C$786, C66, $D$2:$D$786, D66, $E$2:$E$786, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O66"/>
@@ -16475,7 +16475,7 @@
         <v>300</v>
       </c>
       <c r="N67" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B67, $C$2:$C$786, C67, $D$2:$D$786, D67, $E$2:$E$786, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O67"/>
@@ -16515,7 +16515,7 @@
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B68, $C$2:$C$786, C68, $D$2:$D$786, D68, $E$2:$E$786, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68"/>
@@ -16553,7 +16553,7 @@
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B69, $C$2:$C$786, C69, $D$2:$D$786, D69, $E$2:$E$786, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O69"/>
@@ -16591,7 +16591,7 @@
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B70, $C$2:$C$786, C70, $D$2:$D$786, D70, $E$2:$E$786, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O70"/>
@@ -16629,7 +16629,7 @@
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
       <c r="N71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B71, $C$2:$C$786, C71, $D$2:$D$786, D71, $E$2:$E$786, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O71"/>
@@ -16667,7 +16667,7 @@
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B72, $C$2:$C$786, C72, $D$2:$D$786, D72, $E$2:$E$786, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O72"/>
@@ -16705,7 +16705,7 @@
       <c r="L73" s="17"/>
       <c r="M73" s="17"/>
       <c r="N73" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B73, $C$2:$C$786, C73, $D$2:$D$786, D73, $E$2:$E$786, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O73"/>
@@ -16753,7 +16753,7 @@
         <v>540</v>
       </c>
       <c r="N74" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B74, $C$2:$C$786, C74, $D$2:$D$786, D74, $E$2:$E$786, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O74"/>
@@ -16795,7 +16795,7 @@
       <c r="L75" s="17"/>
       <c r="M75" s="17"/>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B75, $C$2:$C$786, C75, $D$2:$D$786, D75, $E$2:$E$786, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O75"/>
@@ -16833,7 +16833,7 @@
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B76, $C$2:$C$786, C76, $D$2:$D$786, D76, $E$2:$E$786, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O76"/>
@@ -16880,7 +16880,7 @@
         <v>442</v>
       </c>
       <c r="N77" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B77, $C$2:$C$786, C77, $D$2:$D$786, D77, $E$2:$E$786, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O77"/>
@@ -16918,7 +16918,7 @@
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B78, $C$2:$C$786, C78, $D$2:$D$786, D78, $E$2:$E$786, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78"/>
@@ -16958,7 +16958,7 @@
       <c r="L79" s="17"/>
       <c r="M79" s="17"/>
       <c r="N79" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B79, $C$2:$C$786, C79, $D$2:$D$786, D79, $E$2:$E$786, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O79"/>
@@ -16996,7 +16996,7 @@
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
       <c r="N80" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B80, $C$2:$C$786, C80, $D$2:$D$786, D80, $E$2:$E$786, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O80"/>
@@ -17036,7 +17036,7 @@
       <c r="L81" s="17"/>
       <c r="M81" s="17"/>
       <c r="N81" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B81, $C$2:$C$786, C81, $D$2:$D$786, D81, $E$2:$E$786, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O81"/>
@@ -17076,7 +17076,7 @@
       <c r="L82" s="17"/>
       <c r="M82" s="17"/>
       <c r="N82" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B82, $C$2:$C$786, C82, $D$2:$D$786, D82, $E$2:$E$786, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O82"/>
@@ -17116,7 +17116,7 @@
       <c r="L83" s="17"/>
       <c r="M83" s="17"/>
       <c r="N83" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B83, $C$2:$C$786, C83, $D$2:$D$786, D83, $E$2:$E$786, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O83"/>
@@ -17154,7 +17154,7 @@
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B84, $C$2:$C$786, C84, $D$2:$D$786, D84, $E$2:$E$786, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O84"/>
@@ -17192,7 +17192,7 @@
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
       <c r="N85" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B85, $C$2:$C$786, C85, $D$2:$D$786, D85, $E$2:$E$786, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O85"/>
@@ -17230,7 +17230,7 @@
       <c r="L86" s="17"/>
       <c r="M86" s="17"/>
       <c r="N86" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B86, $C$2:$C$786, C86, $D$2:$D$786, D86, $E$2:$E$786, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O86"/>
@@ -17268,7 +17268,7 @@
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
       <c r="N87" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B87, $C$2:$C$786, C87, $D$2:$D$786, D87, $E$2:$E$786, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O87"/>
@@ -17306,7 +17306,7 @@
       <c r="L88" s="17"/>
       <c r="M88" s="17"/>
       <c r="N88" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B88, $C$2:$C$786, C88, $D$2:$D$786, D88, $E$2:$E$786, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O88"/>
@@ -17344,7 +17344,7 @@
       <c r="L89" s="17"/>
       <c r="M89" s="17"/>
       <c r="N89" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B89, $C$2:$C$786, C89, $D$2:$D$786, D89, $E$2:$E$786, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O89"/>
@@ -17384,7 +17384,7 @@
       <c r="L90" s="17"/>
       <c r="M90" s="17"/>
       <c r="N90" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B90, $C$2:$C$786, C90, $D$2:$D$786, D90, $E$2:$E$786, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O90"/>
@@ -17422,7 +17422,7 @@
       <c r="L91" s="17"/>
       <c r="M91" s="17"/>
       <c r="N91" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B91, $C$2:$C$786, C91, $D$2:$D$786, D91, $E$2:$E$786, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O91"/>
@@ -17460,7 +17460,7 @@
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
       <c r="N92" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B92, $C$2:$C$786, C92, $D$2:$D$786, D92, $E$2:$E$786, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O92"/>
@@ -17498,7 +17498,7 @@
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
       <c r="N93" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B93, $C$2:$C$786, C93, $D$2:$D$786, D93, $E$2:$E$786, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O93"/>
@@ -17536,7 +17536,7 @@
       <c r="L94" s="17"/>
       <c r="M94" s="17"/>
       <c r="N94" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B94, $C$2:$C$786, C94, $D$2:$D$786, D94, $E$2:$E$786, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O94"/>
@@ -17574,7 +17574,7 @@
       <c r="L95" s="17"/>
       <c r="M95" s="17"/>
       <c r="N95" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B95, $C$2:$C$786, C95, $D$2:$D$786, D95, $E$2:$E$786, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O95"/>
@@ -17612,7 +17612,7 @@
       <c r="L96" s="17"/>
       <c r="M96" s="17"/>
       <c r="N96" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B96, $C$2:$C$786, C96, $D$2:$D$786, D96, $E$2:$E$786, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O96"/>
@@ -17650,7 +17650,7 @@
       <c r="L97" s="17"/>
       <c r="M97" s="17"/>
       <c r="N97" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B97, $C$2:$C$786, C97, $D$2:$D$786, D97, $E$2:$E$786, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O97"/>
@@ -17688,7 +17688,7 @@
       <c r="L98" s="17"/>
       <c r="M98" s="17"/>
       <c r="N98" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B98, $C$2:$C$786, C98, $D$2:$D$786, D98, $E$2:$E$786, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O98"/>
@@ -17728,7 +17728,7 @@
       <c r="L99" s="17"/>
       <c r="M99" s="17"/>
       <c r="N99" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B99, $C$2:$C$786, C99, $D$2:$D$786, D99, $E$2:$E$786, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O99"/>
@@ -17765,7 +17765,7 @@
         <v>118</v>
       </c>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B100, $C$2:$C$786, C100, $D$2:$D$786, D100, $E$2:$E$786, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O100" s="47" t="s">
@@ -17810,11 +17810,11 @@
         <v>5755</v>
       </c>
       <c r="M101" s="33">
-        <f t="shared" ref="M101:M118" si="0">ABS((D101*E101)-L101)</f>
+        <f t="shared" ref="M101:M118" si="2">ABS((D101*E101)-L101)</f>
         <v>275</v>
       </c>
       <c r="N101" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B101, $C$2:$C$786, C101, $D$2:$D$786, D101, $E$2:$E$786, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O101" s="47" t="s">
@@ -17859,11 +17859,11 @@
         <v>5805</v>
       </c>
       <c r="M102" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>225</v>
       </c>
       <c r="N102" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B102, $C$2:$C$786, C102, $D$2:$D$786, D102, $E$2:$E$786, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O102" s="47" t="s">
@@ -17908,11 +17908,11 @@
         <v>15050</v>
       </c>
       <c r="M103" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>430</v>
       </c>
       <c r="N103" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B103, $C$2:$C$786, C103, $D$2:$D$786, D103, $E$2:$E$786, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O103" s="47" t="s">
@@ -17957,11 +17957,11 @@
         <v>8480</v>
       </c>
       <c r="M104" s="27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>280</v>
       </c>
       <c r="N104" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B104, $C$2:$C$786, C104, $D$2:$D$786, D104, $E$2:$E$786, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O104" s="47" t="s">
@@ -18006,11 +18006,11 @@
         <v>5940</v>
       </c>
       <c r="M105" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B105, $C$2:$C$786, C105, $D$2:$D$786, D105, $E$2:$E$786, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O105" s="47" t="s">
@@ -18055,11 +18055,11 @@
         <v>3005</v>
       </c>
       <c r="M106" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>240</v>
       </c>
       <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B106, $C$2:$C$786, C106, $D$2:$D$786, D106, $E$2:$E$786, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18101,11 +18101,11 @@
         <v>20010</v>
       </c>
       <c r="M107" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>450</v>
       </c>
       <c r="N107" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B107, $C$2:$C$786, C107, $D$2:$D$786, D107, $E$2:$E$786, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O107" s="47" t="s">
@@ -18150,11 +18150,11 @@
         <v>4080</v>
       </c>
       <c r="M108" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N108" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B108, $C$2:$C$786, C108, $D$2:$D$786, D108, $E$2:$E$786, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18196,11 +18196,11 @@
         <v>12510</v>
       </c>
       <c r="M109" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>290</v>
       </c>
       <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B109, $C$2:$C$786, C109, $D$2:$D$786, D109, $E$2:$E$786, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="10"/>
@@ -18243,11 +18243,11 @@
         <v>16219.999999999998</v>
       </c>
       <c r="M110" s="27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300.00000000000182</v>
       </c>
       <c r="N110" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B110, $C$2:$C$786, C110, $D$2:$D$786, D110, $E$2:$E$786, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O110" s="10"/>
@@ -18290,11 +18290,11 @@
         <v>6334</v>
       </c>
       <c r="M111" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>274</v>
       </c>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B111, $C$2:$C$786, C111, $D$2:$D$786, D111, $E$2:$E$786, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O111" s="10"/>
@@ -18337,11 +18337,11 @@
         <v>25300</v>
       </c>
       <c r="M112" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>650</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B112, $C$2:$C$786, C112, $D$2:$D$786, D112, $E$2:$E$786, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O112" s="47" t="s">
@@ -18386,11 +18386,11 @@
         <v>12480</v>
       </c>
       <c r="M113" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>495</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B113, $C$2:$C$786, C113, $D$2:$D$786, D113, $E$2:$E$786, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O113" s="47" t="s">
@@ -18435,11 +18435,11 @@
         <v>55382.5</v>
       </c>
       <c r="M114" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1567.5</v>
       </c>
       <c r="N114" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B114, $C$2:$C$786, C114, $D$2:$D$786, D114, $E$2:$E$786, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O114" s="47" t="s">
@@ -18484,11 +18484,11 @@
         <v>20260</v>
       </c>
       <c r="M115" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N115" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B115, $C$2:$C$786, C115, $D$2:$D$786, D115, $E$2:$E$786, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18530,11 +18530,11 @@
         <v>8220</v>
       </c>
       <c r="M116" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>360</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B116, $C$2:$C$786, C116, $D$2:$D$786, D116, $E$2:$E$786, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O116" s="47" t="s">
@@ -18579,11 +18579,11 @@
         <v>9270</v>
       </c>
       <c r="M117" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B117, $C$2:$C$786, C117, $D$2:$D$786, D117, $E$2:$E$786, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="47" t="s">
@@ -18628,11 +18628,11 @@
         <v>5905</v>
       </c>
       <c r="M118" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>275</v>
       </c>
       <c r="N118" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B118, $C$2:$C$786, C118, $D$2:$D$786, D118, $E$2:$E$786, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="10"/>
@@ -18672,7 +18672,7 @@
       <c r="L119" s="18"/>
       <c r="M119" s="18"/>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B119, $C$2:$C$786, C119, $D$2:$D$786, D119, $E$2:$E$786, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O119" s="47" t="s">
@@ -18721,7 +18721,7 @@
         <v>300</v>
       </c>
       <c r="N120" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B120, $C$2:$C$786, C120, $D$2:$D$786, D120, $E$2:$E$786, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O120" s="47" t="s">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="J121" s="40"/>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B121, $C$2:$C$786, C121, $D$2:$D$786, D121, $E$2:$E$786, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18800,11 +18800,11 @@
         <v>18800</v>
       </c>
       <c r="M122" s="18">
-        <f t="shared" ref="M122:M127" si="1">ABS((D122*E122)-L122)</f>
+        <f t="shared" ref="M122:M127" si="3">ABS((D122*E122)-L122)</f>
         <v>500</v>
       </c>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B122, $C$2:$C$786, C122, $D$2:$D$786, D122, $E$2:$E$786, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O122" s="48" t="s">
@@ -18849,11 +18849,11 @@
         <v>4120</v>
       </c>
       <c r="M123" s="18">
+        <f t="shared" si="3"/>
+        <v>270</v>
+      </c>
+      <c r="N123" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>270</v>
-      </c>
-      <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B123, $C$2:$C$786, C123, $D$2:$D$786, D123, $E$2:$E$786, E123) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O123" s="48" t="s">
@@ -18898,11 +18898,11 @@
         <v>15075</v>
       </c>
       <c r="M124" s="18">
+        <f t="shared" si="3"/>
+        <v>645</v>
+      </c>
+      <c r="N124" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>645</v>
-      </c>
-      <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B124, $C$2:$C$786, C124, $D$2:$D$786, D124, $E$2:$E$786, E124) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O124" s="10"/>
@@ -18945,11 +18945,11 @@
         <v>25530</v>
       </c>
       <c r="M125" s="18">
+        <f t="shared" si="3"/>
+        <v>650</v>
+      </c>
+      <c r="N125" t="str">
         <f t="shared" si="1"/>
-        <v>650</v>
-      </c>
-      <c r="N125" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B125, $C$2:$C$786, C125, $D$2:$D$786, D125, $E$2:$E$786, E125) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O125"/>
@@ -18992,11 +18992,11 @@
         <v>32200</v>
       </c>
       <c r="M126" s="18">
+        <f t="shared" si="3"/>
+        <v>1200</v>
+      </c>
+      <c r="N126" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>1200</v>
-      </c>
-      <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B126, $C$2:$C$786, C126, $D$2:$D$786, D126, $E$2:$E$786, E126) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O126" s="47" t="s">
@@ -19041,11 +19041,11 @@
         <v>12600</v>
       </c>
       <c r="M127" s="18">
+        <f t="shared" si="3"/>
+        <v>360</v>
+      </c>
+      <c r="N127" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>360</v>
-      </c>
-      <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B127, $C$2:$C$786, C127, $D$2:$D$786, D127, $E$2:$E$786, E127) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -19079,7 +19079,7 @@
       </c>
       <c r="J128" s="40"/>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B128, $C$2:$C$786, C128, $D$2:$D$786, D128, $E$2:$E$786, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="47" t="s">
@@ -19124,11 +19124,11 @@
         <v>14552</v>
       </c>
       <c r="M129" s="18">
-        <f t="shared" ref="M129:M137" si="2">ABS((D129*E129)-L129)</f>
+        <f t="shared" ref="M129:M137" si="4">ABS((D129*E129)-L129)</f>
         <v>300</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B129, $C$2:$C$786, C129, $D$2:$D$786, D129, $E$2:$E$786, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O129" s="47" t="s">
@@ -19173,11 +19173,11 @@
         <v>3560</v>
       </c>
       <c r="M130" s="33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>175</v>
       </c>
       <c r="N130" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B130, $C$2:$C$786, C130, $D$2:$D$786, D130, $E$2:$E$786, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="5">IF(COUNTIFS( $B$2:$B$786, B130, $C$2:$C$786, C130, $D$2:$D$786, D130, $E$2:$E$786, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O130" s="47" t="s">
@@ -19222,11 +19222,11 @@
         <v>3510</v>
       </c>
       <c r="M131" s="33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>225</v>
       </c>
       <c r="N131" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B131, $C$2:$C$786, C131, $D$2:$D$786, D131, $E$2:$E$786, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O131" s="47" t="s">
@@ -19271,11 +19271,11 @@
         <v>8810</v>
       </c>
       <c r="M132" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>650</v>
       </c>
       <c r="N132" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B132, $C$2:$C$786, C132, $D$2:$D$786, D132, $E$2:$E$786, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O132" s="47" t="s">
@@ -19320,11 +19320,11 @@
         <v>14440</v>
       </c>
       <c r="M133" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B133, $C$2:$C$786, C133, $D$2:$D$786, D133, $E$2:$E$786, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O133"/>
@@ -19367,11 +19367,11 @@
         <v>15075</v>
       </c>
       <c r="M134" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>525</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B134, $C$2:$C$786, C134, $D$2:$D$786, D134, $E$2:$E$786, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19413,11 +19413,11 @@
         <v>26020</v>
       </c>
       <c r="M135" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>340</v>
       </c>
       <c r="N135" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B135, $C$2:$C$786, C135, $D$2:$D$786, D135, $E$2:$E$786, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19459,11 +19459,11 @@
         <v>6105</v>
       </c>
       <c r="M136" s="33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>150</v>
       </c>
       <c r="N136" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B136, $C$2:$C$786, C136, $D$2:$D$786, D136, $E$2:$E$786, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O136" s="10"/>
@@ -19506,11 +19506,11 @@
         <v>6005</v>
       </c>
       <c r="M137" s="33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
       <c r="N137" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B137, $C$2:$C$786, C137, $D$2:$D$786, D137, $E$2:$E$786, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="J138" s="40"/>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B138, $C$2:$C$786, C138, $D$2:$D$786, D138, $E$2:$E$786, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O138" s="25"/>
@@ -19591,7 +19591,7 @@
         <v>300</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B139, $C$2:$C$786, C139, $D$2:$D$786, D139, $E$2:$E$786, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O139" s="10"/>
@@ -19638,7 +19638,7 @@
         <v>268</v>
       </c>
       <c r="N140" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B140, $C$2:$C$786, C140, $D$2:$D$786, D140, $E$2:$E$786, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O140" s="47" t="s">
@@ -19687,7 +19687,7 @@
         <v>250</v>
       </c>
       <c r="N141" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B141, $C$2:$C$786, C141, $D$2:$D$786, D141, $E$2:$E$786, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19733,7 +19733,7 @@
         <v>300</v>
       </c>
       <c r="N142" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B142, $C$2:$C$786, C142, $D$2:$D$786, D142, $E$2:$E$786, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="J143" s="40"/>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B143, $C$2:$C$786, C143, $D$2:$D$786, D143, $E$2:$E$786, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19809,11 +19809,11 @@
         <v>10300</v>
       </c>
       <c r="M144" s="18">
-        <f t="shared" ref="M144:M152" si="3">ABS((D144*E144)-L144)</f>
+        <f t="shared" ref="M144:M152" si="6">ABS((D144*E144)-L144)</f>
         <v>300</v>
       </c>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B144, $C$2:$C$786, C144, $D$2:$D$786, D144, $E$2:$E$786, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19855,11 +19855,11 @@
         <v>26180</v>
       </c>
       <c r="M145" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B145, $C$2:$C$786, C145, $D$2:$D$786, D145, $E$2:$E$786, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19901,11 +19901,11 @@
         <v>18140</v>
       </c>
       <c r="M146" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>650</v>
       </c>
       <c r="N146" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B146, $C$2:$C$786, C146, $D$2:$D$786, D146, $E$2:$E$786, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O146" s="47" t="s">
@@ -19950,11 +19950,11 @@
         <v>9470</v>
       </c>
       <c r="M147" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B147, $C$2:$C$786, C147, $D$2:$D$786, D147, $E$2:$E$786, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19996,11 +19996,11 @@
         <v>32900</v>
       </c>
       <c r="M148" s="33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1000</v>
       </c>
       <c r="N148" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B148, $C$2:$C$786, C148, $D$2:$D$786, D148, $E$2:$E$786, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O148" s="26"/>
@@ -20043,11 +20043,11 @@
         <v>33200</v>
       </c>
       <c r="M149" s="33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>700</v>
       </c>
       <c r="N149" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B149, $C$2:$C$786, C149, $D$2:$D$786, D149, $E$2:$E$786, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -20089,11 +20089,11 @@
         <v>26300</v>
       </c>
       <c r="M150" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N150" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B150, $C$2:$C$786, C150, $D$2:$D$786, D150, $E$2:$E$786, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20135,11 +20135,11 @@
         <v>17040</v>
       </c>
       <c r="M151" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>880</v>
       </c>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B151, $C$2:$C$786, C151, $D$2:$D$786, D151, $E$2:$E$786, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20181,11 +20181,11 @@
         <v>12800</v>
       </c>
       <c r="M152" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>400</v>
       </c>
       <c r="N152" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B152, $C$2:$C$786, C152, $D$2:$D$786, D152, $E$2:$E$786, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20226,7 +20226,7 @@
       <c r="L153" s="17"/>
       <c r="M153" s="17"/>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B153, $C$2:$C$786, C153, $D$2:$D$786, D153, $E$2:$E$786, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20272,7 +20272,7 @@
         <v>650</v>
       </c>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B154, $C$2:$C$786, C154, $D$2:$D$786, D154, $E$2:$E$786, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20318,7 +20318,7 @@
         <v>934</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B155, $C$2:$C$786, C155, $D$2:$D$786, D155, $E$2:$E$786, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20364,7 +20364,7 @@
         <v>295</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B156, $C$2:$C$786, C156, $D$2:$D$786, D156, $E$2:$E$786, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20410,7 +20410,7 @@
         <v>300</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B157, $C$2:$C$786, C157, $D$2:$D$786, D157, $E$2:$E$786, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O157" s="35"/>
@@ -20447,7 +20447,7 @@
         <v>117</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B158, $C$2:$C$786, C158, $D$2:$D$786, D158, $E$2:$E$786, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20493,7 +20493,7 @@
         <v>250</v>
       </c>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B159, $C$2:$C$786, C159, $D$2:$D$786, D159, $E$2:$E$786, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
         <v>250</v>
       </c>
       <c r="N160" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B160, $C$2:$C$786, C160, $D$2:$D$786, D160, $E$2:$E$786, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20575,7 +20575,7 @@
         <v>201</v>
       </c>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B161, $C$2:$C$786, C161, $D$2:$D$786, D161, $E$2:$E$786, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20621,7 +20621,7 @@
         <v>294</v>
       </c>
       <c r="N162" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B162, $C$2:$C$786, C162, $D$2:$D$786, D162, $E$2:$E$786, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -20667,7 +20667,7 @@
         <v>294</v>
       </c>
       <c r="N163" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B163, $C$2:$C$786, C163, $D$2:$D$786, D163, $E$2:$E$786, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -20713,7 +20713,7 @@
         <v>280</v>
       </c>
       <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B164, $C$2:$C$786, C164, $D$2:$D$786, D164, $E$2:$E$786, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20747,7 +20747,7 @@
       </c>
       <c r="J165" s="40"/>
       <c r="N165" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B165, $C$2:$C$786, C165, $D$2:$D$786, D165, $E$2:$E$786, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20783,7 +20783,7 @@
         <v>156</v>
       </c>
       <c r="N166" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B166, $C$2:$C$786, C166, $D$2:$D$786, D166, $E$2:$E$786, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
         <v>117</v>
       </c>
       <c r="N167" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B167, $C$2:$C$786, C167, $D$2:$D$786, D167, $E$2:$E$786, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20855,7 +20855,7 @@
         <v>117</v>
       </c>
       <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B168, $C$2:$C$786, C168, $D$2:$D$786, D168, $E$2:$E$786, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20901,7 +20901,7 @@
         <v>501</v>
       </c>
       <c r="N169" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B169, $C$2:$C$786, C169, $D$2:$D$786, D169, $E$2:$E$786, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O169" s="47" t="s">
@@ -20940,7 +20940,7 @@
         <v>118</v>
       </c>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B170, $C$2:$C$786, C170, $D$2:$D$786, D170, $E$2:$E$786, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O170" s="47" t="s">
@@ -20989,7 +20989,7 @@
         <v>500</v>
       </c>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B171, $C$2:$C$786, C171, $D$2:$D$786, D171, $E$2:$E$786, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O171" s="47" t="s">
@@ -21038,7 +21038,7 @@
         <v>300</v>
       </c>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B172, $C$2:$C$786, C172, $D$2:$D$786, D172, $E$2:$E$786, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21072,7 +21072,7 @@
       </c>
       <c r="J173" s="40"/>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B173, $C$2:$C$786, C173, $D$2:$D$786, D173, $E$2:$E$786, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21108,7 +21108,7 @@
         <v>118</v>
       </c>
       <c r="N174" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B174, $C$2:$C$786, C174, $D$2:$D$786, D174, $E$2:$E$786, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21154,7 +21154,7 @@
         <v>500</v>
       </c>
       <c r="N175" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B175, $C$2:$C$786, C175, $D$2:$D$786, D175, $E$2:$E$786, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21200,7 +21200,7 @@
         <v>300</v>
       </c>
       <c r="N176" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B176, $C$2:$C$786, C176, $D$2:$D$786, D176, $E$2:$E$786, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21246,7 +21246,7 @@
         <v>300</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B177, $C$2:$C$786, C177, $D$2:$D$786, D177, $E$2:$E$786, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21280,7 +21280,7 @@
       </c>
       <c r="J178" s="40"/>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B178, $C$2:$C$786, C178, $D$2:$D$786, D178, $E$2:$E$786, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21316,7 +21316,7 @@
         <v>117</v>
       </c>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B179, $C$2:$C$786, C179, $D$2:$D$786, D179, $E$2:$E$786, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21362,7 +21362,7 @@
         <v>370</v>
       </c>
       <c r="N180" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B180, $C$2:$C$786, C180, $D$2:$D$786, D180, $E$2:$E$786, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21408,7 +21408,7 @@
         <v>320</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B181, $C$2:$C$786, C181, $D$2:$D$786, D181, $E$2:$E$786, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
         <v>448</v>
       </c>
       <c r="N182" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B182, $C$2:$C$786, C182, $D$2:$D$786, D182, $E$2:$E$786, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21500,7 +21500,7 @@
         <v>1000</v>
       </c>
       <c r="N183" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B183, $C$2:$C$786, C183, $D$2:$D$786, D183, $E$2:$E$786, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O183" s="47" t="s">
@@ -21542,7 +21542,7 @@
         <v>144</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B184, $C$2:$C$786, C184, $D$2:$D$786, D184, $E$2:$E$786, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21576,7 +21576,7 @@
       </c>
       <c r="J185" s="40"/>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B185, $C$2:$C$786, C185, $D$2:$D$786, D185, $E$2:$E$786, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
         <v>118</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B186, $C$2:$C$786, C186, $D$2:$D$786, D186, $E$2:$E$786, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21658,7 +21658,7 @@
         <v>700</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B187, $C$2:$C$786, C187, $D$2:$D$786, D187, $E$2:$E$786, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21704,7 +21704,7 @@
         <v>527.5</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B188, $C$2:$C$786, C188, $D$2:$D$786, D188, $E$2:$E$786, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21743,7 +21743,7 @@
         <v>143</v>
       </c>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B189, $C$2:$C$786, C189, $D$2:$D$786, D189, $E$2:$E$786, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21779,7 +21779,7 @@
         <v>117</v>
       </c>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B190, $C$2:$C$786, C190, $D$2:$D$786, D190, $E$2:$E$786, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21813,7 +21813,7 @@
       </c>
       <c r="J191" s="40"/>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B191, $C$2:$C$786, C191, $D$2:$D$786, D191, $E$2:$E$786, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O191" s="35"/>
@@ -21860,7 +21860,7 @@
         <v>300</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B192, $C$2:$C$786, C192, $D$2:$D$786, D192, $E$2:$E$786, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21906,7 +21906,7 @@
         <v>188</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B193, $C$2:$C$786, C193, $D$2:$D$786, D193, $E$2:$E$786, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21952,7 +21952,7 @@
         <v>300</v>
       </c>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B194, $C$2:$C$786, C194, $D$2:$D$786, D194, $E$2:$E$786, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="7">IF(COUNTIFS( $B$2:$B$786, B194, $C$2:$C$786, C194, $D$2:$D$786, D194, $E$2:$E$786, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -21998,7 +21998,7 @@
         <v>1800</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B195, $C$2:$C$786, C195, $D$2:$D$786, D195, $E$2:$E$786, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22032,7 +22032,7 @@
       </c>
       <c r="J196" s="40"/>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B196, $C$2:$C$786, C196, $D$2:$D$786, D196, $E$2:$E$786, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22078,7 +22078,7 @@
         <v>300</v>
       </c>
       <c r="N197" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B197, $C$2:$C$786, C197, $D$2:$D$786, D197, $E$2:$E$786, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22124,7 +22124,7 @@
         <v>260</v>
       </c>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B198, $C$2:$C$786, C198, $D$2:$D$786, D198, $E$2:$E$786, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
         <v>117</v>
       </c>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B199, $C$2:$C$786, C199, $D$2:$D$786, D199, $E$2:$E$786, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22196,7 +22196,7 @@
         <v>55</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B200, $C$2:$C$786, C200, $D$2:$D$786, D200, $E$2:$E$786, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22230,7 +22230,7 @@
       </c>
       <c r="J201" s="40"/>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B201, $C$2:$C$786, C201, $D$2:$D$786, D201, $E$2:$E$786, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22264,7 +22264,7 @@
       </c>
       <c r="J202" s="40"/>
       <c r="N202" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B202, $C$2:$C$786, C202, $D$2:$D$786, D202, $E$2:$E$786, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22310,7 +22310,7 @@
         <v>140</v>
       </c>
       <c r="N203" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B203, $C$2:$C$786, C203, $D$2:$D$786, D203, $E$2:$E$786, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -22356,7 +22356,7 @@
         <v>300</v>
       </c>
       <c r="N204" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B204, $C$2:$C$786, C204, $D$2:$D$786, D204, $E$2:$E$786, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -22402,7 +22402,7 @@
         <v>940</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B205, $C$2:$C$786, C205, $D$2:$D$786, D205, $E$2:$E$786, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22448,7 +22448,7 @@
         <v>300</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B206, $C$2:$C$786, C206, $D$2:$D$786, D206, $E$2:$E$786, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22494,7 +22494,7 @@
         <v>260</v>
       </c>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B207, $C$2:$C$786, C207, $D$2:$D$786, D207, $E$2:$E$786, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22531,7 +22531,7 @@
       <c r="L208" s="18"/>
       <c r="M208" s="18"/>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B208, $C$2:$C$786, C208, $D$2:$D$786, D208, $E$2:$E$786, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O208" s="10"/>
@@ -22566,7 +22566,7 @@
       </c>
       <c r="J209" s="40"/>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B209, $C$2:$C$786, C209, $D$2:$D$786, D209, $E$2:$E$786, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22602,7 +22602,7 @@
         <v>117</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B210, $C$2:$C$786, C210, $D$2:$D$786, D210, $E$2:$E$786, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22638,7 +22638,7 @@
         <v>117</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B211, $C$2:$C$786, C211, $D$2:$D$786, D211, $E$2:$E$786, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22677,7 +22677,7 @@
         <v>145</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B212, $C$2:$C$786, C212, $D$2:$D$786, D212, $E$2:$E$786, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22711,7 +22711,7 @@
       </c>
       <c r="J213" s="40"/>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B213, $C$2:$C$786, C213, $D$2:$D$786, D213, $E$2:$E$786, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22747,7 +22747,7 @@
         <v>118</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B214, $C$2:$C$786, C214, $D$2:$D$786, D214, $E$2:$E$786, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22793,7 +22793,7 @@
         <v>250</v>
       </c>
       <c r="N215" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B215, $C$2:$C$786, C215, $D$2:$D$786, D215, $E$2:$E$786, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22832,7 +22832,7 @@
       <c r="L216" s="18"/>
       <c r="M216" s="18"/>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B216, $C$2:$C$786, C216, $D$2:$D$786, D216, $E$2:$E$786, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O216" s="10"/>
@@ -22867,7 +22867,7 @@
       </c>
       <c r="J217" s="40"/>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B217, $C$2:$C$786, C217, $D$2:$D$786, D217, $E$2:$E$786, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22903,7 +22903,7 @@
         <v>117</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B218, $C$2:$C$786, C218, $D$2:$D$786, D218, $E$2:$E$786, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22939,7 +22939,7 @@
         <v>118</v>
       </c>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B219, $C$2:$C$786, C219, $D$2:$D$786, D219, $E$2:$E$786, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22975,7 +22975,7 @@
         <v>118</v>
       </c>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B220, $C$2:$C$786, C220, $D$2:$D$786, D220, $E$2:$E$786, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23021,7 +23021,7 @@
         <v>800</v>
       </c>
       <c r="N221" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B221, $C$2:$C$786, C221, $D$2:$D$786, D221, $E$2:$E$786, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O221" s="10"/>
@@ -23061,7 +23061,7 @@
       <c r="L222" s="18"/>
       <c r="M222" s="18"/>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B222, $C$2:$C$786, C222, $D$2:$D$786, D222, $E$2:$E$786, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O222" s="10"/>
@@ -23098,7 +23098,7 @@
         <v>118</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B223, $C$2:$C$786, C223, $D$2:$D$786, D223, $E$2:$E$786, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O223" s="35"/>
@@ -23133,7 +23133,7 @@
       </c>
       <c r="J224" s="40"/>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B224, $C$2:$C$786, C224, $D$2:$D$786, D224, $E$2:$E$786, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O224" s="35"/>
@@ -23170,7 +23170,7 @@
         <v>117</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B225, $C$2:$C$786, C225, $D$2:$D$786, D225, $E$2:$E$786, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23206,7 +23206,7 @@
         <v>55</v>
       </c>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B226, $C$2:$C$786, C226, $D$2:$D$786, D226, $E$2:$E$786, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23252,7 +23252,7 @@
         <v>300</v>
       </c>
       <c r="N227" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B227, $C$2:$C$786, C227, $D$2:$D$786, D227, $E$2:$E$786, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23298,7 +23298,7 @@
         <v>650</v>
       </c>
       <c r="N228" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B228, $C$2:$C$786, C228, $D$2:$D$786, D228, $E$2:$E$786, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23344,7 +23344,7 @@
         <v>650</v>
       </c>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B229, $C$2:$C$786, C229, $D$2:$D$786, D229, $E$2:$E$786, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O229" s="35"/>
@@ -23391,7 +23391,7 @@
         <v>285</v>
       </c>
       <c r="N230" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B230, $C$2:$C$786, C230, $D$2:$D$786, D230, $E$2:$E$786, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23437,7 +23437,7 @@
         <v>726</v>
       </c>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B231, $C$2:$C$786, C231, $D$2:$D$786, D231, $E$2:$E$786, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="J232" s="40"/>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B232, $C$2:$C$786, C232, $D$2:$D$786, D232, $E$2:$E$786, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23510,7 +23510,7 @@
         <v>146</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B233, $C$2:$C$786, C233, $D$2:$D$786, D233, $E$2:$E$786, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23546,7 +23546,7 @@
         <v>118</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B234, $C$2:$C$786, C234, $D$2:$D$786, D234, $E$2:$E$786, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O234" s="35"/>
@@ -23581,7 +23581,7 @@
       </c>
       <c r="J235" s="40"/>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B235, $C$2:$C$786, C235, $D$2:$D$786, D235, $E$2:$E$786, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23615,7 +23615,7 @@
       </c>
       <c r="J236" s="40"/>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B236, $C$2:$C$786, C236, $D$2:$D$786, D236, $E$2:$E$786, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23661,7 +23661,7 @@
         <v>275</v>
       </c>
       <c r="N237" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B237, $C$2:$C$786, C237, $D$2:$D$786, D237, $E$2:$E$786, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23697,7 +23697,7 @@
         <v>118</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B238, $C$2:$C$786, C238, $D$2:$D$786, D238, $E$2:$E$786, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23743,7 +23743,7 @@
         <v>300</v>
       </c>
       <c r="N239" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B239, $C$2:$C$786, C239, $D$2:$D$786, D239, $E$2:$E$786, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="J240" s="40"/>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B240, $C$2:$C$786, C240, $D$2:$D$786, D240, $E$2:$E$786, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23813,7 +23813,7 @@
         <v>118</v>
       </c>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B241, $C$2:$C$786, C241, $D$2:$D$786, D241, $E$2:$E$786, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23847,7 +23847,7 @@
       </c>
       <c r="J242" s="40"/>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B242, $C$2:$C$786, C242, $D$2:$D$786, D242, $E$2:$E$786, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23893,7 +23893,7 @@
         <v>250</v>
       </c>
       <c r="N243" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B243, $C$2:$C$786, C243, $D$2:$D$786, D243, $E$2:$E$786, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23939,7 +23939,7 @@
         <v>480</v>
       </c>
       <c r="N244" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B244, $C$2:$C$786, C244, $D$2:$D$786, D244, $E$2:$E$786, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O244" s="10"/>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="J245" s="40"/>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B245, $C$2:$C$786, C245, $D$2:$D$786, D245, $E$2:$E$786, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24010,7 +24010,7 @@
         <v>117</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B246, $C$2:$C$786, C246, $D$2:$D$786, D246, $E$2:$E$786, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24044,7 +24044,7 @@
       </c>
       <c r="J247" s="40"/>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B247, $C$2:$C$786, C247, $D$2:$D$786, D247, $E$2:$E$786, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24078,7 +24078,7 @@
       </c>
       <c r="J248" s="40"/>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B248, $C$2:$C$786, C248, $D$2:$D$786, D248, $E$2:$E$786, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24115,7 +24115,7 @@
       <c r="L249" s="18"/>
       <c r="M249" s="18"/>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B249, $C$2:$C$786, C249, $D$2:$D$786, D249, $E$2:$E$786, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O249" s="10"/>
@@ -24150,7 +24150,7 @@
       </c>
       <c r="J250" s="40"/>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B250, $C$2:$C$786, C250, $D$2:$D$786, D250, $E$2:$E$786, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24186,7 +24186,7 @@
         <v>118</v>
       </c>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B251, $C$2:$C$786, C251, $D$2:$D$786, D251, $E$2:$E$786, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O251" s="35"/>
@@ -24233,7 +24233,7 @@
         <v>300</v>
       </c>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B252, $C$2:$C$786, C252, $D$2:$D$786, D252, $E$2:$E$786, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24269,7 +24269,7 @@
         <v>118</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B253, $C$2:$C$786, C253, $D$2:$D$786, D253, $E$2:$E$786, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24303,7 +24303,7 @@
       </c>
       <c r="J254" s="40"/>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B254, $C$2:$C$786, C254, $D$2:$D$786, D254, $E$2:$E$786, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24337,7 +24337,7 @@
       </c>
       <c r="J255" s="40"/>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B255, $C$2:$C$786, C255, $D$2:$D$786, D255, $E$2:$E$786, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24373,7 +24373,7 @@
         <v>118</v>
       </c>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B256, $C$2:$C$786, C256, $D$2:$D$786, D256, $E$2:$E$786, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24407,7 +24407,7 @@
       </c>
       <c r="J257" s="40"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B257, $C$2:$C$786, C257, $D$2:$D$786, D257, $E$2:$E$786, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O257" s="35"/>
@@ -24454,7 +24454,7 @@
         <v>250</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B258, $C$2:$C$786, C258, $D$2:$D$786, D258, $E$2:$E$786, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N283" si="8">IF(COUNTIFS( $B$2:$B$786, B258, $C$2:$C$786, C258, $D$2:$D$786, D258, $E$2:$E$786, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -24488,7 +24488,7 @@
       </c>
       <c r="J259" s="40"/>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B259, $C$2:$C$786, C259, $D$2:$D$786, D259, $E$2:$E$786, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24522,7 +24522,7 @@
       </c>
       <c r="J260" s="40"/>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B260, $C$2:$C$786, C260, $D$2:$D$786, D260, $E$2:$E$786, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24556,7 +24556,7 @@
       </c>
       <c r="J261" s="40"/>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B261, $C$2:$C$786, C261, $D$2:$D$786, D261, $E$2:$E$786, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="J262" s="40"/>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B262, $C$2:$C$786, C262, $D$2:$D$786, D262, $E$2:$E$786, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="J263" s="40"/>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B263, $C$2:$C$786, C263, $D$2:$D$786, D263, $E$2:$E$786, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24658,7 +24658,7 @@
       </c>
       <c r="J264" s="40"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B264, $C$2:$C$786, C264, $D$2:$D$786, D264, $E$2:$E$786, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24692,7 +24692,7 @@
       </c>
       <c r="J265" s="40"/>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B265, $C$2:$C$786, C265, $D$2:$D$786, D265, $E$2:$E$786, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24728,7 +24728,7 @@
         <v>118</v>
       </c>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B266, $C$2:$C$786, C266, $D$2:$D$786, D266, $E$2:$E$786, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24764,7 +24764,7 @@
         <v>55</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B267, $C$2:$C$786, C267, $D$2:$D$786, D267, $E$2:$E$786, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24803,7 +24803,7 @@
       <c r="L268" s="18"/>
       <c r="M268" s="18"/>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B268, $C$2:$C$786, C268, $D$2:$D$786, D268, $E$2:$E$786, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O268" s="10"/>
@@ -24838,7 +24838,7 @@
       </c>
       <c r="J269" s="40"/>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B269, $C$2:$C$786, C269, $D$2:$D$786, D269, $E$2:$E$786, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24872,7 +24872,7 @@
       </c>
       <c r="J270" s="40"/>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B270, $C$2:$C$786, C270, $D$2:$D$786, D270, $E$2:$E$786, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24906,7 +24906,7 @@
       </c>
       <c r="J271" s="40"/>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B271, $C$2:$C$786, C271, $D$2:$D$786, D271, $E$2:$E$786, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24952,7 +24952,7 @@
         <v>250</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B272, $C$2:$C$786, C272, $D$2:$D$786, D272, $E$2:$E$786, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24986,7 +24986,7 @@
       </c>
       <c r="J273" s="40"/>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B273, $C$2:$C$786, C273, $D$2:$D$786, D273, $E$2:$E$786, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25020,7 +25020,7 @@
       </c>
       <c r="J274" s="40"/>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B274, $C$2:$C$786, C274, $D$2:$D$786, D274, $E$2:$E$786, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25054,7 +25054,7 @@
       </c>
       <c r="J275" s="40"/>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B275, $C$2:$C$786, C275, $D$2:$D$786, D275, $E$2:$E$786, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O275" s="35"/>
@@ -25089,7 +25089,7 @@
       </c>
       <c r="J276" s="40"/>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B276, $C$2:$C$786, C276, $D$2:$D$786, D276, $E$2:$E$786, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25123,7 +25123,7 @@
         <v>253</v>
       </c>
       <c r="N277" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B277, $C$2:$C$786, C277, $D$2:$D$786, D277, $E$2:$E$786, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25153,11 +25153,11 @@
         <v>5620</v>
       </c>
       <c r="M278" s="33">
-        <f t="shared" ref="M278:M283" si="4">ABS((D278*E278)-L278)</f>
+        <f t="shared" ref="M278:M283" si="9">ABS((D278*E278)-L278)</f>
         <v>300</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B278, $C$2:$C$786, C278, $D$2:$D$786, D278, $E$2:$E$786, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25187,11 +25187,11 @@
         <v>8570</v>
       </c>
       <c r="M279" s="33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>650</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B279, $C$2:$C$786, C279, $D$2:$D$786, D279, $E$2:$E$786, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25221,11 +25221,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M280" s="33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>620.99999999999636</v>
       </c>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B280, $C$2:$C$786, C280, $D$2:$D$786, D280, $E$2:$E$786, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25255,11 +25255,11 @@
         <v>16580</v>
       </c>
       <c r="M281" s="33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>750</v>
       </c>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B281, $C$2:$C$786, C281, $D$2:$D$786, D281, $E$2:$E$786, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25289,11 +25289,11 @@
         <v>18340</v>
       </c>
       <c r="M282" s="33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>400</v>
       </c>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B282, $C$2:$C$786, C282, $D$2:$D$786, D282, $E$2:$E$786, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25323,11 +25323,11 @@
         <v>19760</v>
       </c>
       <c r="M283" s="33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>500</v>
       </c>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$786, B283, $C$2:$C$786, C283, $D$2:$D$786, D283, $E$2:$E$786, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
